--- a/data_mod_rupiah.xlsx
+++ b/data_mod_rupiah.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfan\Documents\0. Gawean\0. DEN\22. Rupiah\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfan\GitHub\beer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB652E1-D229-4EAF-8B6B-5D435EF8E770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC6220-3622-46EA-AAB7-7E78992743B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{136FD5EA-69F6-4D36-BF21-61416DD08A06}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="2" xr2:uid="{136FD5EA-69F6-4D36-BF21-61416DD08A06}"/>
   </bookViews>
   <sheets>
     <sheet name="data_clean" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="44">
   <si>
     <t>infl_diff</t>
   </si>
@@ -231,7 +231,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,20 +276,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B0F0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -322,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -344,29 +330,46 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF008000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -377,6 +380,91 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>317500</xdr:colOff>
+      <xdr:row>207</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>211</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18FF4AC0-C35C-CDEF-7B18-D34F28007A8A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4759325" y="39420800"/>
+          <a:ext cx="2587625" cy="701675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="FF0000"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg1"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reds: To Be Updated</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-FI" sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="bg1"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6327,7 +6415,7 @@
       </c>
       <c r="D194" s="11">
         <f>Sheet2!H195</f>
-        <v>0.42500503486026187</v>
+        <v>0.4250050348898835</v>
       </c>
       <c r="E194" s="11">
         <f>Sheet2!I195</f>
@@ -6356,7 +6444,7 @@
       </c>
       <c r="D195" s="11">
         <f>Sheet2!H196</f>
-        <v>0.44716985532447973</v>
+        <v>0.44716985535040815</v>
       </c>
       <c r="E195" s="11">
         <f>Sheet2!I196</f>
@@ -6385,7 +6473,7 @@
       </c>
       <c r="D196" s="11">
         <f>Sheet2!H197</f>
-        <v>0.37924192280769342</v>
+        <v>0.37924158366473865</v>
       </c>
       <c r="E196" s="11">
         <f>Sheet2!I197</f>
@@ -6414,7 +6502,7 @@
       </c>
       <c r="D197" s="11">
         <f>Sheet2!H198</f>
-        <v>0.37438231179122305</v>
+        <v>0.44967485490095382</v>
       </c>
       <c r="E197" s="11">
         <f>Sheet2!I198</f>
@@ -6443,7 +6531,7 @@
       </c>
       <c r="D198" s="11">
         <f>Sheet2!H199</f>
-        <v>0.47055615255381672</v>
+        <v>0.46939788848575226</v>
       </c>
       <c r="E198" s="11">
         <f>Sheet2!I199</f>
@@ -6472,7 +6560,7 @@
       </c>
       <c r="D199" s="11">
         <f>Sheet2!H200</f>
-        <v>0.46148385768599987</v>
+        <v>0.46683494089523275</v>
       </c>
       <c r="E199" s="11">
         <f>Sheet2!I200</f>
@@ -6512,10 +6600,10 @@
       <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="25"/>
+      <c r="D1" s="22"/>
       <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
@@ -6614,10 +6702,10 @@
       <c r="M3" s="6">
         <v>191.34247619047619</v>
       </c>
-      <c r="O3" s="24">
+      <c r="O3" s="20">
         <v>9365</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="20">
         <v>9285.6666666666661</v>
       </c>
     </row>
@@ -6668,10 +6756,10 @@
       <c r="M4" s="6">
         <v>202.83085000000003</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="20">
         <v>9335</v>
       </c>
-      <c r="P4" s="24">
+      <c r="P4" s="20">
         <v>9344.9</v>
       </c>
     </row>
@@ -6722,10 +6810,10 @@
       <c r="M5" s="6">
         <v>163.08356521739125</v>
       </c>
-      <c r="O5" s="24">
+      <c r="O5" s="20">
         <v>9115</v>
       </c>
-      <c r="P5" s="24">
+      <c r="P5" s="20">
         <v>9167</v>
       </c>
     </row>
@@ -6776,10 +6864,10 @@
       <c r="M6" s="6">
         <v>159.84154545454547</v>
       </c>
-      <c r="O6" s="24">
+      <c r="O6" s="20">
         <v>9012</v>
       </c>
-      <c r="P6" s="24">
+      <c r="P6" s="20">
         <v>9030.4090909090901</v>
       </c>
     </row>
@@ -6830,10 +6918,10 @@
       <c r="M7" s="6">
         <v>186.46042857142854</v>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="20">
         <v>9180</v>
       </c>
-      <c r="P7" s="24">
+      <c r="P7" s="20">
         <v>9172.9047619047615</v>
       </c>
     </row>
@@ -6884,10 +6972,10 @@
       <c r="M8" s="6">
         <v>182.34554545454546</v>
       </c>
-      <c r="O8" s="24">
+      <c r="O8" s="20">
         <v>9083</v>
       </c>
-      <c r="P8" s="24">
+      <c r="P8" s="20">
         <v>9146.2727272727279</v>
       </c>
     </row>
@@ -6938,10 +7026,10 @@
       <c r="M9" s="6">
         <v>166.68695454545457</v>
       </c>
-      <c r="O9" s="24">
+      <c r="O9" s="20">
         <v>8952</v>
       </c>
-      <c r="P9" s="24">
+      <c r="P9" s="20">
         <v>9041.318181818182</v>
       </c>
     </row>
@@ -6992,10 +7080,10 @@
       <c r="M10" s="6">
         <v>152.44131818181816</v>
       </c>
-      <c r="O10" s="24">
+      <c r="O10" s="20">
         <v>9041</v>
       </c>
-      <c r="P10" s="24">
+      <c r="P10" s="20">
         <v>8972.4090909090901</v>
       </c>
     </row>
@@ -7046,10 +7134,10 @@
       <c r="M11" s="6">
         <v>149.64409090909092</v>
       </c>
-      <c r="O11" s="24">
+      <c r="O11" s="20">
         <v>8924</v>
       </c>
-      <c r="P11" s="24">
+      <c r="P11" s="20">
         <v>8974.181818181818</v>
       </c>
     </row>
@@ -7100,10 +7188,10 @@
       <c r="M12" s="6">
         <v>131.21904761904761</v>
       </c>
-      <c r="O12" s="24">
+      <c r="O12" s="20">
         <v>8928</v>
       </c>
-      <c r="P12" s="24">
+      <c r="P12" s="20">
         <v>8930.0476190476184</v>
       </c>
     </row>
@@ -7154,10 +7242,10 @@
       <c r="M13" s="6">
         <v>137.55540909090908</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="20">
         <v>9013</v>
       </c>
-      <c r="P13" s="24">
+      <c r="P13" s="20">
         <v>8943.363636363636</v>
       </c>
     </row>
@@ -7208,10 +7296,10 @@
       <c r="M14" s="6">
         <v>131.19230434782611</v>
       </c>
-      <c r="O14" s="24">
+      <c r="O14" s="20">
         <v>8991</v>
       </c>
-      <c r="P14" s="24">
+      <c r="P14" s="20">
         <v>9025</v>
       </c>
     </row>
@@ -7262,10 +7350,10 @@
       <c r="M15" s="6">
         <v>141.62828571428571</v>
       </c>
-      <c r="O15" s="24">
+      <c r="O15" s="20">
         <v>9057</v>
       </c>
-      <c r="P15" s="24">
+      <c r="P15" s="20">
         <v>9037.4761904761908</v>
       </c>
     </row>
@@ -7316,10 +7404,10 @@
       <c r="M16" s="6">
         <v>151.89179999999999</v>
       </c>
-      <c r="O16" s="24">
+      <c r="O16" s="20">
         <v>8823</v>
       </c>
-      <c r="P16" s="24">
+      <c r="P16" s="20">
         <v>8918.7999999999993</v>
       </c>
     </row>
@@ -7370,10 +7458,10 @@
       <c r="M17" s="6">
         <v>145.0194347826087</v>
       </c>
-      <c r="O17" s="24">
+      <c r="O17" s="20">
         <v>8709</v>
       </c>
-      <c r="P17" s="24">
+      <c r="P17" s="20">
         <v>8762.217391304348</v>
       </c>
     </row>
@@ -7424,10 +7512,10 @@
       <c r="M18" s="6">
         <v>139.65299999999999</v>
       </c>
-      <c r="O18" s="24">
+      <c r="O18" s="20">
         <v>8574</v>
       </c>
-      <c r="P18" s="24">
+      <c r="P18" s="20">
         <v>8650.5238095238092</v>
       </c>
     </row>
@@ -7478,10 +7566,10 @@
       <c r="M19" s="6">
         <v>134.52895454545455</v>
       </c>
-      <c r="O19" s="24">
+      <c r="O19" s="20">
         <v>8537</v>
       </c>
-      <c r="P19" s="24">
+      <c r="P19" s="20">
         <v>8560.318181818182</v>
       </c>
     </row>
@@ -7532,10 +7620,10 @@
       <c r="M20" s="6">
         <v>138.42363636363635</v>
       </c>
-      <c r="O20" s="24">
+      <c r="O20" s="20">
         <v>8597</v>
       </c>
-      <c r="P20" s="24">
+      <c r="P20" s="20">
         <v>8565.4090909090901</v>
       </c>
     </row>
@@ -7586,10 +7674,10 @@
       <c r="M21" s="6">
         <v>137.48757142857144</v>
       </c>
-      <c r="O21" s="24">
+      <c r="O21" s="20">
         <v>8508</v>
       </c>
-      <c r="P21" s="24">
+      <c r="P21" s="20">
         <v>8530.7619047619046</v>
       </c>
     </row>
@@ -7640,10 +7728,10 @@
       <c r="M22" s="6">
         <v>159.51395652173909</v>
       </c>
-      <c r="O22" s="24">
+      <c r="O22" s="20">
         <v>8578</v>
       </c>
-      <c r="P22" s="24">
+      <c r="P22" s="20">
         <v>8529.173913043478</v>
       </c>
     </row>
@@ -7694,10 +7782,10 @@
       <c r="M23" s="6">
         <v>212.14381818181812</v>
       </c>
-      <c r="O23" s="24">
+      <c r="O23" s="20">
         <v>8823</v>
       </c>
-      <c r="P23" s="24">
+      <c r="P23" s="20">
         <v>8729.454545454546</v>
       </c>
     </row>
@@ -7748,10 +7836,10 @@
       <c r="M24" s="6">
         <v>245.83776190476189</v>
       </c>
-      <c r="O24" s="24">
+      <c r="O24" s="20">
         <v>8835</v>
       </c>
-      <c r="P24" s="24">
+      <c r="P24" s="20">
         <v>8865.3333333333339</v>
       </c>
     </row>
@@ -7802,10 +7890,10 @@
       <c r="M25" s="6">
         <v>218.20772727272725</v>
       </c>
-      <c r="O25" s="24">
+      <c r="O25" s="20">
         <v>9170</v>
       </c>
-      <c r="P25" s="24">
+      <c r="P25" s="20">
         <v>9005</v>
       </c>
     </row>
@@ -7856,10 +7944,10 @@
       <c r="M26" s="6">
         <v>208.92922727272725</v>
       </c>
-      <c r="O26" s="24">
+      <c r="O26" s="20">
         <v>9068</v>
       </c>
-      <c r="P26" s="24">
+      <c r="P26" s="20">
         <v>9067.0909090909099</v>
       </c>
     </row>
@@ -7910,10 +7998,10 @@
       <c r="M27" s="6">
         <v>203.43472727272726</v>
       </c>
-      <c r="O27" s="24">
+      <c r="O27" s="20">
         <v>9000</v>
       </c>
-      <c r="P27" s="24">
+      <c r="P27" s="20">
         <v>9066.863636363636</v>
       </c>
     </row>
@@ -7964,10 +8052,10 @@
       <c r="M28" s="6">
         <v>162.49876190476192</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="20">
         <v>9085</v>
       </c>
-      <c r="P28" s="24">
+      <c r="P28" s="20">
         <v>9035.6666666666661</v>
       </c>
     </row>
@@ -8018,10 +8106,10 @@
       <c r="M29" s="6">
         <v>160.37854545454545</v>
       </c>
-      <c r="O29" s="24">
+      <c r="O29" s="20">
         <v>9180</v>
       </c>
-      <c r="P29" s="24">
+      <c r="P29" s="20">
         <v>9158.045454545454</v>
       </c>
     </row>
@@ -8072,10 +8160,10 @@
       <c r="M30" s="6">
         <v>170.10085714285717</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="20">
         <v>9190</v>
       </c>
-      <c r="P30" s="24">
+      <c r="P30" s="20">
         <v>9175</v>
       </c>
     </row>
@@ -8126,10 +8214,10 @@
       <c r="M31" s="6">
         <v>202.28491304347821</v>
       </c>
-      <c r="O31" s="24">
+      <c r="O31" s="20">
         <v>9565</v>
       </c>
-      <c r="P31" s="24">
+      <c r="P31" s="20">
         <v>9316.5217391304341</v>
       </c>
     </row>
@@ -8180,10 +8268,10 @@
       <c r="M32" s="6">
         <v>211.08776190476189</v>
       </c>
-      <c r="O32" s="24">
+      <c r="O32" s="20">
         <v>9480</v>
       </c>
-      <c r="P32" s="24">
+      <c r="P32" s="20">
         <v>9431.6190476190477</v>
       </c>
     </row>
@@ -8234,10 +8322,10 @@
       <c r="M33" s="6">
         <v>183.33040909090911</v>
       </c>
-      <c r="O33" s="24">
+      <c r="O33" s="20">
         <v>9485</v>
       </c>
-      <c r="P33" s="24">
+      <c r="P33" s="20">
         <v>9441.181818181818</v>
       </c>
     </row>
@@ -8288,10 +8376,10 @@
       <c r="M34" s="6">
         <v>174.69426086956523</v>
       </c>
-      <c r="O34" s="24">
+      <c r="O34" s="20">
         <v>9560</v>
       </c>
-      <c r="P34" s="24">
+      <c r="P34" s="20">
         <v>9505.434782608696</v>
       </c>
     </row>
@@ -8342,10 +8430,10 @@
       <c r="M35" s="6">
         <v>168.10974999999999</v>
       </c>
-      <c r="O35" s="24">
+      <c r="O35" s="20">
         <v>9588</v>
       </c>
-      <c r="P35" s="24">
+      <c r="P35" s="20">
         <v>9564.7999999999993</v>
       </c>
     </row>
@@ -8396,10 +8484,10 @@
       <c r="M36" s="6">
         <v>165.55799999999999</v>
       </c>
-      <c r="O36" s="24">
+      <c r="O36" s="20">
         <v>9615</v>
       </c>
-      <c r="P36" s="24">
+      <c r="P36" s="20">
         <v>9599.2608695652179</v>
       </c>
     </row>
@@ -8450,10 +8538,10 @@
       <c r="M37" s="6">
         <v>165.55799999999999</v>
       </c>
-      <c r="O37" s="24">
+      <c r="O37" s="20">
         <v>9605</v>
       </c>
-      <c r="P37" s="24">
+      <c r="P37" s="20">
         <v>9620.136363636364</v>
       </c>
     </row>
@@ -8504,10 +8592,10 @@
       <c r="M38" s="6">
         <v>133.89519047619044</v>
       </c>
-      <c r="O38" s="24">
+      <c r="O38" s="20">
         <v>9670</v>
       </c>
-      <c r="P38" s="24">
+      <c r="P38" s="20">
         <v>9646.0476190476184</v>
       </c>
     </row>
@@ -8558,10 +8646,10 @@
       <c r="M39" s="6">
         <v>134.6097391304348</v>
       </c>
-      <c r="O39" s="24">
+      <c r="O39" s="20">
         <v>9698</v>
       </c>
-      <c r="P39" s="24">
+      <c r="P39" s="20">
         <v>9654.3043478260861</v>
       </c>
     </row>
@@ -8612,10 +8700,10 @@
       <c r="M40" s="6">
         <v>142.51524999999998</v>
       </c>
-      <c r="O40" s="24">
+      <c r="O40" s="20">
         <v>9667</v>
       </c>
-      <c r="P40" s="24">
+      <c r="P40" s="20">
         <v>9680.75</v>
       </c>
     </row>
@@ -8666,10 +8754,10 @@
       <c r="M41" s="6">
         <v>139.25942857142857</v>
       </c>
-      <c r="O41" s="24">
+      <c r="O41" s="20">
         <v>9719</v>
       </c>
-      <c r="P41" s="24">
+      <c r="P41" s="20">
         <v>9708.4285714285706</v>
       </c>
     </row>
@@ -8720,10 +8808,10 @@
       <c r="M42" s="6">
         <v>146.49922727272727</v>
       </c>
-      <c r="O42" s="24">
+      <c r="O42" s="20">
         <v>9722</v>
       </c>
-      <c r="P42" s="24">
+      <c r="P42" s="20">
         <v>9723.636363636364</v>
       </c>
     </row>
@@ -8774,10 +8862,10 @@
       <c r="M43" s="6">
         <v>137.90939130434782</v>
       </c>
-      <c r="O43" s="24">
+      <c r="O43" s="20">
         <v>9802</v>
       </c>
-      <c r="P43" s="24">
+      <c r="P43" s="20">
         <v>9759.652173913044</v>
       </c>
     </row>
@@ -8828,10 +8916,10 @@
       <c r="M44" s="6">
         <v>211.74079999999995</v>
       </c>
-      <c r="O44" s="24">
+      <c r="O44" s="20">
         <v>9929</v>
       </c>
-      <c r="P44" s="24">
+      <c r="P44" s="20">
         <v>9871.7000000000007</v>
       </c>
     </row>
@@ -8882,10 +8970,10 @@
       <c r="M45" s="6">
         <v>208.34808695652183</v>
       </c>
-      <c r="O45" s="24">
+      <c r="O45" s="20">
         <v>10278</v>
       </c>
-      <c r="P45" s="24">
+      <c r="P45" s="20">
         <v>10071.478260869566</v>
       </c>
     </row>
@@ -8936,10 +9024,10 @@
       <c r="M46" s="6">
         <v>244.53031818181816</v>
       </c>
-      <c r="O46" s="24">
+      <c r="O46" s="20">
         <v>10924</v>
       </c>
-      <c r="P46" s="24">
+      <c r="P46" s="20">
         <v>10532.545454545454</v>
       </c>
     </row>
@@ -8990,10 +9078,10 @@
       <c r="M47" s="6">
         <v>281.72300000000001</v>
       </c>
-      <c r="O47" s="24">
+      <c r="O47" s="20">
         <v>11613</v>
       </c>
-      <c r="P47" s="24">
+      <c r="P47" s="20">
         <v>11327.476190476191</v>
       </c>
     </row>
@@ -9044,10 +9132,10 @@
       <c r="M48" s="6">
         <v>262.24773913043481</v>
       </c>
-      <c r="O48" s="24">
+      <c r="O48" s="20">
         <v>11234</v>
       </c>
-      <c r="P48" s="24">
+      <c r="P48" s="20">
         <v>11345.130434782608</v>
       </c>
     </row>
@@ -9098,10 +9186,10 @@
       <c r="M49" s="6">
         <v>223.61804761904764</v>
       </c>
-      <c r="O49" s="24">
+      <c r="O49" s="20">
         <v>11977</v>
       </c>
-      <c r="P49" s="24">
+      <c r="P49" s="20">
         <v>11610.666666666666</v>
       </c>
     </row>
@@ -9152,10 +9240,10 @@
       <c r="M50" s="6">
         <v>224.41749999999999</v>
       </c>
-      <c r="O50" s="24">
+      <c r="O50" s="20">
         <v>12189</v>
       </c>
-      <c r="P50" s="24">
+      <c r="P50" s="20">
         <v>12086.727272727272</v>
       </c>
     </row>
@@ -9206,10 +9294,10 @@
       <c r="M51" s="6">
         <v>228.61734782608693</v>
       </c>
-      <c r="O51" s="24">
+      <c r="O51" s="20">
         <v>12226</v>
       </c>
-      <c r="P51" s="24">
+      <c r="P51" s="20">
         <v>12158.347826086956</v>
       </c>
     </row>
@@ -9260,10 +9348,10 @@
       <c r="M52" s="6">
         <v>209.85519999999997</v>
       </c>
-      <c r="O52" s="24">
+      <c r="O52" s="20">
         <v>11634</v>
       </c>
-      <c r="P52" s="24">
+      <c r="P52" s="20">
         <v>11919.8</v>
       </c>
     </row>
@@ -9314,10 +9402,10 @@
       <c r="M53" s="6">
         <v>181.97395238095237</v>
       </c>
-      <c r="O53" s="24">
+      <c r="O53" s="20">
         <v>11404</v>
       </c>
-      <c r="P53" s="24">
+      <c r="P53" s="20">
         <v>11416.857142857143</v>
       </c>
     </row>
@@ -9368,10 +9456,10 @@
       <c r="M54" s="6">
         <v>171.83245454545451</v>
       </c>
-      <c r="O54" s="24">
+      <c r="O54" s="20">
         <v>11532</v>
       </c>
-      <c r="P54" s="24">
+      <c r="P54" s="20">
         <v>11431.545454545454</v>
       </c>
     </row>
@@ -9422,10 +9510,10 @@
       <c r="M55" s="6">
         <v>155.29827272727269</v>
       </c>
-      <c r="O55" s="24">
+      <c r="O55" s="20">
         <v>11611</v>
       </c>
-      <c r="P55" s="24">
+      <c r="P55" s="20">
         <v>11536.272727272728</v>
       </c>
     </row>
@@ -9476,10 +9564,10 @@
       <c r="M56" s="6">
         <v>147.9182857142857</v>
       </c>
-      <c r="O56" s="24">
+      <c r="O56" s="20">
         <v>11969</v>
       </c>
-      <c r="P56" s="24">
+      <c r="P56" s="20">
         <v>11892.523809523809</v>
       </c>
     </row>
@@ -9530,10 +9618,10 @@
       <c r="M57" s="6">
         <v>148.47921739130433</v>
       </c>
-      <c r="O57" s="24">
+      <c r="O57" s="20">
         <v>11591</v>
       </c>
-      <c r="P57" s="24">
+      <c r="P57" s="20">
         <v>11663.608695652174</v>
       </c>
     </row>
@@ -9584,10 +9672,10 @@
       <c r="M58" s="6">
         <v>147.81885714285713</v>
       </c>
-      <c r="O58" s="24">
+      <c r="O58" s="20">
         <v>11717</v>
       </c>
-      <c r="P58" s="24">
+      <c r="P58" s="20">
         <v>11710.904761904761</v>
       </c>
     </row>
@@ -9638,10 +9726,10 @@
       <c r="M59" s="6">
         <v>140.39736363636365</v>
       </c>
-      <c r="O59" s="24">
+      <c r="O59" s="20">
         <v>12212</v>
       </c>
-      <c r="P59" s="24">
+      <c r="P59" s="20">
         <v>11898.59090909091</v>
       </c>
     </row>
@@ -9692,10 +9780,10 @@
       <c r="M60" s="6">
         <v>162.09878260869564</v>
       </c>
-      <c r="O60" s="24">
+      <c r="O60" s="20">
         <v>12082</v>
       </c>
-      <c r="P60" s="24">
+      <c r="P60" s="20">
         <v>12142.04347826087</v>
       </c>
     </row>
@@ -9746,10 +9834,10 @@
       <c r="M61" s="6">
         <v>141.33325000000002</v>
       </c>
-      <c r="O61" s="24">
+      <c r="O61" s="20">
         <v>12196</v>
       </c>
-      <c r="P61" s="24">
+      <c r="P61" s="20">
         <v>12166.9</v>
       </c>
     </row>
@@ -9800,10 +9888,10 @@
       <c r="M62" s="6">
         <v>160.62560869565223</v>
       </c>
-      <c r="O62" s="24">
+      <c r="O62" s="20">
         <v>12440</v>
       </c>
-      <c r="P62" s="24">
+      <c r="P62" s="20">
         <v>12431.565217391304</v>
       </c>
     </row>
@@ -9854,10 +9942,10 @@
       <c r="M63" s="6">
         <v>163.68454545454549</v>
       </c>
-      <c r="O63" s="24">
+      <c r="O63" s="20">
         <v>12625</v>
       </c>
-      <c r="P63" s="24">
+      <c r="P63" s="20">
         <v>12573.59090909091</v>
       </c>
     </row>
@@ -9908,10 +9996,10 @@
       <c r="M64" s="6">
         <v>150.06445000000002</v>
       </c>
-      <c r="O64" s="24">
+      <c r="O64" s="20">
         <v>12863</v>
       </c>
-      <c r="P64" s="24">
+      <c r="P64" s="20">
         <v>12762.75</v>
       </c>
     </row>
@@ -9962,10 +10050,10 @@
       <c r="M65" s="6">
         <v>152.01759090909093</v>
       </c>
-      <c r="O65" s="24">
+      <c r="O65" s="20">
         <v>13084</v>
       </c>
-      <c r="P65" s="24">
+      <c r="P65" s="20">
         <v>13067.363636363636</v>
       </c>
     </row>
@@ -10016,10 +10104,10 @@
       <c r="M66" s="6">
         <v>157.65195454545452</v>
       </c>
-      <c r="O66" s="24">
+      <c r="O66" s="20">
         <v>12937</v>
       </c>
-      <c r="P66" s="24">
+      <c r="P66" s="20">
         <v>12947.59090909091</v>
       </c>
     </row>
@@ -10070,10 +10158,10 @@
       <c r="M67" s="6">
         <v>164.48228571428569</v>
       </c>
-      <c r="O67" s="24">
+      <c r="O67" s="20">
         <v>13211</v>
       </c>
-      <c r="P67" s="24">
+      <c r="P67" s="20">
         <v>13133.238095238095</v>
       </c>
     </row>
@@ -10124,10 +10212,10 @@
       <c r="M68" s="6">
         <v>172.51095454545452</v>
       </c>
-      <c r="O68" s="24">
+      <c r="O68" s="20">
         <v>13332</v>
       </c>
-      <c r="P68" s="24">
+      <c r="P68" s="20">
         <v>13305.90909090909</v>
       </c>
     </row>
@@ -10178,10 +10266,10 @@
       <c r="M69" s="6">
         <v>172.86465217391304</v>
       </c>
-      <c r="O69" s="24">
+      <c r="O69" s="20">
         <v>13481</v>
       </c>
-      <c r="P69" s="24">
+      <c r="P69" s="20">
         <v>13376.565217391304</v>
       </c>
     </row>
@@ -10232,10 +10320,10 @@
       <c r="M70" s="6">
         <v>211.23342857142862</v>
       </c>
-      <c r="O70" s="24">
+      <c r="O70" s="20">
         <v>14027</v>
       </c>
-      <c r="P70" s="24">
+      <c r="P70" s="20">
         <v>13789.952380952382</v>
       </c>
     </row>
@@ -10286,10 +10374,10 @@
       <c r="M71" s="6">
         <v>246.19090909090912</v>
       </c>
-      <c r="O71" s="24">
+      <c r="O71" s="20">
         <v>14657</v>
       </c>
-      <c r="P71" s="24">
+      <c r="P71" s="20">
         <v>14411.045454545454</v>
       </c>
     </row>
@@ -10340,10 +10428,10 @@
       <c r="M72" s="6">
         <v>228.3147727272727</v>
       </c>
-      <c r="O72" s="24">
+      <c r="O72" s="20">
         <v>13639</v>
       </c>
-      <c r="P72" s="24">
+      <c r="P72" s="20">
         <v>13777.59090909091</v>
       </c>
     </row>
@@ -10394,10 +10482,10 @@
       <c r="M73" s="6">
         <v>217.1787619047619</v>
       </c>
-      <c r="O73" s="24">
+      <c r="O73" s="20">
         <v>13840</v>
       </c>
-      <c r="P73" s="24">
+      <c r="P73" s="20">
         <v>13677.333333333334</v>
       </c>
     </row>
@@ -10448,10 +10536,10 @@
       <c r="M74" s="6">
         <v>236.62921739130437</v>
       </c>
-      <c r="O74" s="24">
+      <c r="O74" s="20">
         <v>13795</v>
       </c>
-      <c r="P74" s="24">
+      <c r="P74" s="20">
         <v>13836.173913043478</v>
       </c>
     </row>
@@ -10502,10 +10590,10 @@
       <c r="M75" s="6">
         <v>244.64495238095242</v>
       </c>
-      <c r="O75" s="24">
+      <c r="O75" s="20">
         <v>13846</v>
       </c>
-      <c r="P75" s="24">
+      <c r="P75" s="20">
         <v>13887.190476190477</v>
       </c>
     </row>
@@ -10556,10 +10644,10 @@
       <c r="M76" s="6">
         <v>243.35871428571434</v>
       </c>
-      <c r="O76" s="24">
+      <c r="O76" s="20">
         <v>13395</v>
       </c>
-      <c r="P76" s="24">
+      <c r="P76" s="20">
         <v>13513.380952380952</v>
       </c>
     </row>
@@ -10610,10 +10698,10 @@
       <c r="M77" s="6">
         <v>204.34500000000003</v>
       </c>
-      <c r="O77" s="24">
+      <c r="O77" s="20">
         <v>13276</v>
       </c>
-      <c r="P77" s="24">
+      <c r="P77" s="20">
         <v>13198.826086956522</v>
       </c>
     </row>
@@ -10664,10 +10752,10 @@
       <c r="M78" s="6">
         <v>198.41947619047616</v>
       </c>
-      <c r="O78" s="24">
+      <c r="O78" s="20">
         <v>13204</v>
       </c>
-      <c r="P78" s="24">
+      <c r="P78" s="20">
         <v>13172.857142857143</v>
       </c>
     </row>
@@ -10718,10 +10806,10 @@
       <c r="M79" s="6">
         <v>190.16877272727277</v>
       </c>
-      <c r="O79" s="24">
+      <c r="O79" s="20">
         <v>13615</v>
       </c>
-      <c r="P79" s="24">
+      <c r="P79" s="20">
         <v>13416.90909090909</v>
       </c>
     </row>
@@ -10772,10 +10860,10 @@
       <c r="M80" s="6">
         <v>192.41354545454544</v>
       </c>
-      <c r="O80" s="24">
+      <c r="O80" s="20">
         <v>13180</v>
       </c>
-      <c r="P80" s="24">
+      <c r="P80" s="20">
         <v>13338.045454545454</v>
       </c>
     </row>
@@ -10826,10 +10914,10 @@
       <c r="M81" s="6">
         <v>168.7737619047619</v>
       </c>
-      <c r="O81" s="24">
+      <c r="O81" s="20">
         <v>13094</v>
       </c>
-      <c r="P81" s="24">
+      <c r="P81" s="20">
         <v>13117.619047619048</v>
       </c>
     </row>
@@ -10880,10 +10968,10 @@
       <c r="M82" s="6">
         <v>146.45617391304344</v>
       </c>
-      <c r="O82" s="24">
+      <c r="O82" s="20">
         <v>13300</v>
       </c>
-      <c r="P82" s="24">
+      <c r="P82" s="20">
         <v>13160.608695652174</v>
       </c>
     </row>
@@ -10934,10 +11022,10 @@
       <c r="M83" s="6">
         <v>145.49236363636365</v>
       </c>
-      <c r="O83" s="24">
+      <c r="O83" s="20">
         <v>12998</v>
       </c>
-      <c r="P83" s="24">
+      <c r="P83" s="20">
         <v>13110</v>
       </c>
     </row>
@@ -10988,10 +11076,10 @@
       <c r="M84" s="6">
         <v>151.74176190476194</v>
       </c>
-      <c r="O84" s="24">
+      <c r="O84" s="20">
         <v>13051</v>
       </c>
-      <c r="P84" s="24">
+      <c r="P84" s="20">
         <v>13018.380952380952</v>
       </c>
     </row>
@@ -11042,10 +11130,10 @@
       <c r="M85" s="6">
         <v>170.87813636363637</v>
       </c>
-      <c r="O85" s="24">
+      <c r="O85" s="20">
         <v>13563</v>
       </c>
-      <c r="P85" s="24">
+      <c r="P85" s="20">
         <v>13314.954545454546</v>
       </c>
     </row>
@@ -11096,10 +11184,10 @@
       <c r="M86" s="6">
         <v>163.19881818181821</v>
       </c>
-      <c r="O86" s="24">
+      <c r="O86" s="20">
         <v>13436</v>
       </c>
-      <c r="P86" s="24">
+      <c r="P86" s="20">
         <v>13409.818181818182</v>
       </c>
     </row>
@@ -11150,10 +11238,10 @@
       <c r="M87" s="6">
         <v>151.86809090909094</v>
       </c>
-      <c r="O87" s="24">
+      <c r="O87" s="20">
         <v>13343</v>
       </c>
-      <c r="P87" s="24">
+      <c r="P87" s="20">
         <v>13366.09090909091</v>
       </c>
     </row>
@@ -11204,10 +11292,10 @@
       <c r="M88" s="6">
         <v>136.8956</v>
       </c>
-      <c r="O88" s="24">
+      <c r="O88" s="20">
         <v>13347</v>
       </c>
-      <c r="P88" s="24">
+      <c r="P88" s="20">
         <v>13337.75</v>
       </c>
     </row>
@@ -11258,10 +11346,10 @@
       <c r="M89" s="6">
         <v>128.88608695652175</v>
       </c>
-      <c r="O89" s="24">
+      <c r="O89" s="20">
         <v>13321</v>
       </c>
-      <c r="P89" s="24">
+      <c r="P89" s="20">
         <v>13343.260869565218</v>
       </c>
     </row>
@@ -11312,10 +11400,10 @@
       <c r="M90" s="6">
         <v>131.84299999999999</v>
       </c>
-      <c r="O90" s="24">
+      <c r="O90" s="20">
         <v>13327</v>
       </c>
-      <c r="P90" s="24">
+      <c r="P90" s="20">
         <v>13302.2</v>
       </c>
     </row>
@@ -11366,10 +11454,10 @@
       <c r="M91" s="6">
         <v>125.85113043478263</v>
       </c>
-      <c r="O91" s="24">
+      <c r="O91" s="20">
         <v>13321</v>
       </c>
-      <c r="P91" s="24">
+      <c r="P91" s="20">
         <v>13322.565217391304</v>
       </c>
     </row>
@@ -11420,10 +11508,10 @@
       <c r="M92" s="6">
         <v>116.95295454545455</v>
       </c>
-      <c r="O92" s="24">
+      <c r="O92" s="20">
         <v>13319</v>
       </c>
-      <c r="P92" s="24">
+      <c r="P92" s="20">
         <v>13307.045454545454</v>
       </c>
     </row>
@@ -11474,10 +11562,10 @@
       <c r="M93" s="6">
         <v>115.39385714285713</v>
       </c>
-      <c r="O93" s="24">
+      <c r="O93" s="20">
         <v>13323</v>
       </c>
-      <c r="P93" s="24">
+      <c r="P93" s="20">
         <v>13346.571428571429</v>
       </c>
     </row>
@@ -11528,10 +11616,10 @@
       <c r="M94" s="6">
         <v>108.89913043478262</v>
       </c>
-      <c r="O94" s="24">
+      <c r="O94" s="20">
         <v>13351</v>
       </c>
-      <c r="P94" s="24">
+      <c r="P94" s="20">
         <v>13343.130434782608</v>
       </c>
     </row>
@@ -11582,10 +11670,10 @@
       <c r="M95" s="6">
         <v>99.948761904761909</v>
       </c>
-      <c r="O95" s="24">
+      <c r="O95" s="20">
         <v>13492</v>
       </c>
-      <c r="P95" s="24">
+      <c r="P95" s="20">
         <v>13307.571428571429</v>
       </c>
     </row>
@@ -11636,10 +11724,10 @@
       <c r="M96" s="6">
         <v>97.784772727272724</v>
       </c>
-      <c r="O96" s="24">
+      <c r="O96" s="20">
         <v>13572</v>
       </c>
-      <c r="P96" s="24">
+      <c r="P96" s="20">
         <v>13528.318181818182</v>
       </c>
     </row>
@@ -11690,10 +11778,10 @@
       <c r="M97" s="6">
         <v>97.763454545454536</v>
       </c>
-      <c r="O97" s="24">
+      <c r="O97" s="20">
         <v>13514</v>
       </c>
-      <c r="P97" s="24">
+      <c r="P97" s="20">
         <v>13527.272727272728</v>
       </c>
     </row>
@@ -11744,10 +11832,10 @@
       <c r="M98" s="6">
         <v>90.532095238095252</v>
       </c>
-      <c r="O98" s="24">
+      <c r="O98" s="20">
         <v>13548</v>
       </c>
-      <c r="P98" s="24">
+      <c r="P98" s="20">
         <v>13559.333333333334</v>
       </c>
     </row>
@@ -11798,10 +11886,10 @@
       <c r="M99" s="6">
         <v>80.348043478260848</v>
       </c>
-      <c r="O99" s="24">
+      <c r="O99" s="20">
         <v>13413</v>
       </c>
-      <c r="P99" s="24">
+      <c r="P99" s="20">
         <v>13388.08695652174</v>
       </c>
     </row>
@@ -11852,10 +11940,10 @@
       <c r="M100" s="6">
         <v>87.574499999999986</v>
       </c>
-      <c r="O100" s="24">
+      <c r="O100" s="20">
         <v>13707</v>
       </c>
-      <c r="P100" s="24">
+      <c r="P100" s="20">
         <v>13601.7</v>
       </c>
     </row>
@@ -11906,10 +11994,10 @@
       <c r="M101" s="6">
         <v>94.428045454545469</v>
       </c>
-      <c r="O101" s="24">
+      <c r="O101" s="20">
         <v>13756</v>
       </c>
-      <c r="P101" s="24">
+      <c r="P101" s="20">
         <v>13760.727272727272</v>
       </c>
     </row>
@@ -11960,10 +12048,10 @@
       <c r="M102" s="6">
         <v>100.70242857142858</v>
       </c>
-      <c r="O102" s="24">
+      <c r="O102" s="20">
         <v>13877</v>
       </c>
-      <c r="P102" s="24">
+      <c r="P102" s="20">
         <v>13809.095238095239</v>
       </c>
     </row>
@@ -12014,10 +12102,10 @@
       <c r="M103" s="6">
         <v>118.39917391304348</v>
       </c>
-      <c r="O103" s="24">
+      <c r="O103" s="20">
         <v>13951</v>
       </c>
-      <c r="P103" s="24">
+      <c r="P103" s="20">
         <v>14038.347826086956</v>
       </c>
     </row>
@@ -12068,10 +12156,10 @@
       <c r="M104" s="6">
         <v>130.93471428571428</v>
       </c>
-      <c r="O104" s="24">
+      <c r="O104" s="20">
         <v>14404</v>
       </c>
-      <c r="P104" s="24">
+      <c r="P104" s="20">
         <v>14007.190476190477</v>
       </c>
     </row>
@@ -12122,10 +12210,10 @@
       <c r="M105" s="6">
         <v>121.41877272727274</v>
       </c>
-      <c r="O105" s="24">
+      <c r="O105" s="20">
         <v>14413</v>
       </c>
-      <c r="P105" s="24">
+      <c r="P105" s="20">
         <v>14410</v>
       </c>
     </row>
@@ -12176,10 +12264,10 @@
       <c r="M106" s="6">
         <v>118.65352173913043</v>
       </c>
-      <c r="O106" s="24">
+      <c r="O106" s="20">
         <v>14711</v>
       </c>
-      <c r="P106" s="24">
+      <c r="P106" s="20">
         <v>14564.91304347826</v>
       </c>
     </row>
@@ -12230,10 +12318,10 @@
       <c r="M107" s="6">
         <v>137.0829</v>
       </c>
-      <c r="O107" s="24">
+      <c r="O107" s="20">
         <v>14929</v>
       </c>
-      <c r="P107" s="24">
+      <c r="P107" s="20">
         <v>14869.7</v>
       </c>
     </row>
@@ -12284,10 +12372,10 @@
       <c r="M108" s="6">
         <v>147.58617391304352</v>
       </c>
-      <c r="O108" s="24">
+      <c r="O108" s="20">
         <v>15227</v>
       </c>
-      <c r="P108" s="24">
+      <c r="P108" s="20">
         <v>15177</v>
       </c>
     </row>
@@ -12338,10 +12426,10 @@
       <c r="M109" s="6">
         <v>148.3783181818182</v>
       </c>
-      <c r="O109" s="24">
+      <c r="O109" s="20">
         <v>14339</v>
       </c>
-      <c r="P109" s="24">
+      <c r="P109" s="20">
         <v>14657.40909090909</v>
       </c>
     </row>
@@ -12392,10 +12480,10 @@
       <c r="M110" s="6">
         <v>138.63090476190479</v>
       </c>
-      <c r="O110" s="24">
+      <c r="O110" s="20">
         <v>14481</v>
       </c>
-      <c r="P110" s="24">
+      <c r="P110" s="20">
         <v>14501.666666666666</v>
       </c>
     </row>
@@ -12446,10 +12534,10 @@
       <c r="M111" s="6">
         <v>127.13008695652169</v>
       </c>
-      <c r="O111" s="24">
+      <c r="O111" s="20">
         <v>14072</v>
       </c>
-      <c r="P111" s="24">
+      <c r="P111" s="20">
         <v>14168.08695652174</v>
       </c>
     </row>
@@ -12500,10 +12588,10 @@
       <c r="M112" s="6">
         <v>110.50135</v>
       </c>
-      <c r="O112" s="24">
+      <c r="O112" s="20">
         <v>14062</v>
       </c>
-      <c r="P112" s="24">
+      <c r="P112" s="20">
         <v>14030.85</v>
       </c>
     </row>
@@ -12554,10 +12642,10 @@
       <c r="M113" s="6">
         <v>91.132571428571424</v>
       </c>
-      <c r="O113" s="24">
+      <c r="O113" s="20">
         <v>14244</v>
       </c>
-      <c r="P113" s="24">
+      <c r="P113" s="20">
         <v>14206.761904761905</v>
       </c>
     </row>
@@ -12608,10 +12696,10 @@
       <c r="M114" s="6">
         <v>95.089272727272743</v>
       </c>
-      <c r="O114" s="24">
+      <c r="O114" s="20">
         <v>14215</v>
       </c>
-      <c r="P114" s="24">
+      <c r="P114" s="20">
         <v>14140.681818181818</v>
       </c>
     </row>
@@ -12662,10 +12750,10 @@
       <c r="M115" s="6">
         <v>104.81430434782605</v>
       </c>
-      <c r="O115" s="24">
+      <c r="O115" s="20">
         <v>14385</v>
       </c>
-      <c r="P115" s="24">
+      <c r="P115" s="20">
         <v>14380.304347826086</v>
       </c>
     </row>
@@ -12716,10 +12804,10 @@
       <c r="M116" s="6">
         <v>104.2079</v>
       </c>
-      <c r="O116" s="24">
+      <c r="O116" s="20">
         <v>14141</v>
       </c>
-      <c r="P116" s="24">
+      <c r="P116" s="20">
         <v>14234.35</v>
       </c>
     </row>
@@ -12770,10 +12858,10 @@
       <c r="M117" s="6">
         <v>87.171434782608685</v>
       </c>
-      <c r="O117" s="24">
+      <c r="O117" s="20">
         <v>14026</v>
       </c>
-      <c r="P117" s="24">
+      <c r="P117" s="20">
         <v>14032.695652173914</v>
       </c>
     </row>
@@ -12824,10 +12912,10 @@
       <c r="M118" s="6">
         <v>92.780863636363634</v>
       </c>
-      <c r="O118" s="24">
+      <c r="O118" s="20">
         <v>14237</v>
       </c>
-      <c r="P118" s="24">
+      <c r="P118" s="20">
         <v>14235.818181818182</v>
       </c>
     </row>
@@ -12878,10 +12966,10 @@
       <c r="M119" s="6">
         <v>78.588523809523792</v>
       </c>
-      <c r="O119" s="24">
+      <c r="O119" s="20">
         <v>14174</v>
       </c>
-      <c r="P119" s="24">
+      <c r="P119" s="20">
         <v>14102.476190476191</v>
       </c>
     </row>
@@ -12932,10 +13020,10 @@
       <c r="M120" s="6">
         <v>85.160739130434791</v>
       </c>
-      <c r="O120" s="24">
+      <c r="O120" s="20">
         <v>14008</v>
       </c>
-      <c r="P120" s="24">
+      <c r="P120" s="20">
         <v>14116.260869565218</v>
       </c>
     </row>
@@ -12986,10 +13074,10 @@
       <c r="M121" s="6">
         <v>73.489999999999981</v>
       </c>
-      <c r="O121" s="24">
+      <c r="O121" s="20">
         <v>14102</v>
       </c>
-      <c r="P121" s="24">
+      <c r="P121" s="20">
         <v>14063.619047619048</v>
       </c>
     </row>
@@ -13040,10 +13128,10 @@
       <c r="M122" s="6">
         <v>69.861227272727277</v>
       </c>
-      <c r="O122" s="24">
+      <c r="O122" s="20">
         <v>13901.004999999999</v>
       </c>
-      <c r="P122" s="24">
+      <c r="P122" s="20">
         <v>14007.5</v>
       </c>
     </row>
@@ -13094,10 +13182,10 @@
       <c r="M123" s="6">
         <v>63.303434782608704</v>
       </c>
-      <c r="O123" s="24">
+      <c r="O123" s="20">
         <v>13662</v>
       </c>
-      <c r="P123" s="24">
+      <c r="P123" s="20">
         <v>13728.434782608696</v>
       </c>
     </row>
@@ -13148,10 +13236,10 @@
       <c r="M124" s="6">
         <v>64.349299999999999</v>
       </c>
-      <c r="O124" s="24">
+      <c r="O124" s="20">
         <v>14234</v>
       </c>
-      <c r="P124" s="24">
+      <c r="P124" s="20">
         <v>13775.3</v>
       </c>
     </row>
@@ -13202,10 +13290,10 @@
       <c r="M125" s="6">
         <v>180.10131818181819</v>
       </c>
-      <c r="O125" s="24">
+      <c r="O125" s="20">
         <v>16367.004999999999</v>
       </c>
-      <c r="P125" s="24">
+      <c r="P125" s="20">
         <v>15245.363636363636</v>
       </c>
     </row>
@@ -13256,10 +13344,10 @@
       <c r="M126" s="6">
         <v>223.14500000000001</v>
       </c>
-      <c r="O126" s="24">
+      <c r="O126" s="20">
         <v>15157.004999999999</v>
       </c>
-      <c r="P126" s="24">
+      <c r="P126" s="20">
         <v>15732.09090909091</v>
       </c>
     </row>
@@ -13310,10 +13398,10 @@
       <c r="M127" s="6">
         <v>194.46928571428575</v>
       </c>
-      <c r="O127" s="24">
+      <c r="O127" s="20">
         <v>14733.004999999999</v>
       </c>
-      <c r="P127" s="24">
+      <c r="P127" s="20">
         <v>14839.619047619048</v>
       </c>
     </row>
@@ -13364,10 +13452,10 @@
       <c r="M128" s="6">
         <v>131.59750000000003</v>
       </c>
-      <c r="O128" s="24">
+      <c r="O128" s="20">
         <v>14302</v>
       </c>
-      <c r="P128" s="24">
+      <c r="P128" s="20">
         <v>14127.90909090909</v>
       </c>
     </row>
@@ -13418,10 +13506,10 @@
       <c r="M129" s="6">
         <v>121.73139130434781</v>
       </c>
-      <c r="O129" s="24">
+      <c r="O129" s="20">
         <v>14653.004999999999</v>
       </c>
-      <c r="P129" s="24">
+      <c r="P129" s="20">
         <v>14535.826086956522</v>
       </c>
     </row>
@@ -13472,10 +13560,10 @@
       <c r="M130" s="6">
         <v>107.16580952380953</v>
       </c>
-      <c r="O130" s="24">
+      <c r="O130" s="20">
         <v>14554</v>
       </c>
-      <c r="P130" s="24">
+      <c r="P130" s="20">
         <v>14689.761904761905</v>
       </c>
     </row>
@@ -13526,10 +13614,10 @@
       <c r="M131" s="6">
         <v>99.105545454545435</v>
       </c>
-      <c r="O131" s="24">
+      <c r="O131" s="20">
         <v>14918</v>
       </c>
-      <c r="P131" s="24">
+      <c r="P131" s="20">
         <v>14807.681818181818</v>
       </c>
     </row>
@@ -13580,10 +13668,10 @@
       <c r="M132" s="6">
         <v>98.591772727272712</v>
       </c>
-      <c r="O132" s="24">
+      <c r="O132" s="20">
         <v>14690</v>
       </c>
-      <c r="P132" s="24">
+      <c r="P132" s="20">
         <v>14697.954545454546</v>
       </c>
     </row>
@@ -13634,10 +13722,10 @@
       <c r="M133" s="6">
         <v>83.181857142857169</v>
       </c>
-      <c r="O133" s="24">
+      <c r="O133" s="20">
         <v>14128</v>
       </c>
-      <c r="P133" s="24">
+      <c r="P133" s="20">
         <v>14201.952380952382</v>
       </c>
     </row>
@@ -13688,10 +13776,10 @@
       <c r="M134" s="6">
         <v>72.282478260869553</v>
       </c>
-      <c r="O134" s="24">
+      <c r="O134" s="20">
         <v>14105.004999999999</v>
       </c>
-      <c r="P134" s="24">
+      <c r="P134" s="20">
         <v>14125.565217391304</v>
       </c>
     </row>
@@ -13742,10 +13830,10 @@
       <c r="M135" s="6">
         <v>71.920428571428587</v>
       </c>
-      <c r="O135" s="24">
+      <c r="O135" s="20">
         <v>14084</v>
       </c>
-      <c r="P135" s="24">
+      <c r="P135" s="20">
         <v>14025.238095238095</v>
       </c>
     </row>
@@ -13796,10 +13884,10 @@
       <c r="M136" s="6">
         <v>73.425099999999972</v>
       </c>
-      <c r="O136" s="24">
+      <c r="O136" s="20">
         <v>14229.004999999999</v>
       </c>
-      <c r="P136" s="24">
+      <c r="P136" s="20">
         <v>14029.45</v>
       </c>
     </row>
@@ -13850,10 +13938,10 @@
       <c r="M137" s="6">
         <v>81.500739130434781</v>
       </c>
-      <c r="O137" s="24">
+      <c r="O137" s="20">
         <v>14572</v>
       </c>
-      <c r="P137" s="24">
+      <c r="P137" s="20">
         <v>14388.217391304348</v>
       </c>
     </row>
@@ -13904,10 +13992,10 @@
       <c r="M138" s="6">
         <v>81.62054545454545</v>
       </c>
-      <c r="O138" s="24">
+      <c r="O138" s="20">
         <v>14468</v>
       </c>
-      <c r="P138" s="24">
+      <c r="P138" s="20">
         <v>14528.818181818182</v>
       </c>
     </row>
@@ -13958,10 +14046,10 @@
       <c r="M139" s="6">
         <v>77.338285714285703</v>
       </c>
-      <c r="O139" s="24">
+      <c r="O139" s="20">
         <v>14310</v>
       </c>
-      <c r="P139" s="24">
+      <c r="P139" s="20">
         <v>14302.333333333334</v>
       </c>
     </row>
@@ -14012,10 +14100,10 @@
       <c r="M140" s="6">
         <v>74.441090909090903</v>
       </c>
-      <c r="O140" s="24">
+      <c r="O140" s="20">
         <v>14496</v>
       </c>
-      <c r="P140" s="24">
+      <c r="P140" s="20">
         <v>14332.045454545454</v>
       </c>
     </row>
@@ -14066,10 +14154,10 @@
       <c r="M141" s="6">
         <v>78.36490909090908</v>
       </c>
-      <c r="O141" s="24">
+      <c r="O141" s="20">
         <v>14491.004999999999</v>
       </c>
-      <c r="P141" s="24">
+      <c r="P141" s="20">
         <v>14495.545454545454</v>
       </c>
     </row>
@@ -14120,10 +14208,10 @@
       <c r="M142" s="6">
         <v>75.069454545454562</v>
       </c>
-      <c r="O142" s="24">
+      <c r="O142" s="20">
         <v>14374</v>
       </c>
-      <c r="P142" s="24">
+      <c r="P142" s="20">
         <v>14378.5</v>
       </c>
     </row>
@@ -14174,10 +14262,10 @@
       <c r="M143" s="6">
         <v>72.857454545454544</v>
       </c>
-      <c r="O143" s="24">
+      <c r="O143" s="20">
         <v>14307.004999999999</v>
       </c>
-      <c r="P143" s="24">
+      <c r="P143" s="20">
         <v>14251.863636363636</v>
       </c>
     </row>
@@ -14228,10 +14316,10 @@
       <c r="M144" s="6">
         <v>85.395809523809532</v>
       </c>
-      <c r="O144" s="24">
+      <c r="O144" s="20">
         <v>14199.004999999999</v>
       </c>
-      <c r="P144" s="24">
+      <c r="P144" s="20">
         <v>14175.761904761905</v>
       </c>
     </row>
@@ -14282,10 +14370,10 @@
       <c r="M145" s="6">
         <v>82.386590909090899</v>
       </c>
-      <c r="O145" s="24">
+      <c r="O145" s="20">
         <v>14340</v>
       </c>
-      <c r="P145" s="24">
+      <c r="P145" s="20">
         <v>14265.59090909091</v>
       </c>
     </row>
@@ -14336,10 +14424,10 @@
       <c r="M146" s="6">
         <v>78.842869565217384</v>
       </c>
-      <c r="O146" s="24">
+      <c r="O146" s="20">
         <v>14269.004999999999</v>
       </c>
-      <c r="P146" s="24">
+      <c r="P146" s="20">
         <v>14322.521739130434</v>
       </c>
     </row>
@@ -14390,10 +14478,10 @@
       <c r="M147" s="6">
         <v>83.264285714285705</v>
       </c>
-      <c r="O147" s="24">
+      <c r="O147" s="20">
         <v>14381.004999999999</v>
       </c>
-      <c r="P147" s="24">
+      <c r="P147" s="20">
         <v>14338</v>
       </c>
     </row>
@@ -14444,10 +14532,10 @@
       <c r="M148" s="6">
         <v>96.822449999999989</v>
       </c>
-      <c r="O148" s="24">
+      <c r="O148" s="20">
         <v>14371.004999999999</v>
       </c>
-      <c r="P148" s="24">
+      <c r="P148" s="20">
         <v>14351.35</v>
       </c>
     </row>
@@ -14498,10 +14586,10 @@
       <c r="M149" s="6">
         <v>103.39260869565216</v>
       </c>
-      <c r="O149" s="24">
+      <c r="O149" s="20">
         <v>14349.004999999999</v>
       </c>
-      <c r="P149" s="24">
+      <c r="P149" s="20">
         <v>14349.04347826087</v>
       </c>
     </row>
@@ -14552,10 +14640,10 @@
       <c r="M150" s="6">
         <v>89.791095238095252</v>
       </c>
-      <c r="O150" s="24">
+      <c r="O150" s="20">
         <v>14418</v>
       </c>
-      <c r="P150" s="24">
+      <c r="P150" s="20">
         <v>14379.428571428571</v>
       </c>
     </row>
@@ -14606,10 +14694,10 @@
       <c r="M151" s="6">
         <v>104.3930909090909</v>
       </c>
-      <c r="O151" s="24">
+      <c r="O151" s="20">
         <v>14544</v>
       </c>
-      <c r="P151" s="24">
+      <c r="P151" s="20">
         <v>14591.818181818182</v>
       </c>
     </row>
@@ -14660,10 +14748,10 @@
       <c r="M152" s="6">
         <v>106.59518181818179</v>
       </c>
-      <c r="O152" s="24">
+      <c r="O152" s="20">
         <v>14848</v>
       </c>
-      <c r="P152" s="24">
+      <c r="P152" s="20">
         <v>14696.318181818182</v>
       </c>
     </row>
@@ -14714,10 +14802,10 @@
       <c r="M153" s="6">
         <v>140.79195238095241</v>
       </c>
-      <c r="O153" s="24">
+      <c r="O153" s="20">
         <v>14958</v>
       </c>
-      <c r="P153" s="24">
+      <c r="P153" s="20">
         <v>14979.571428571429</v>
       </c>
     </row>
@@ -14768,10 +14856,10 @@
       <c r="M154" s="6">
         <v>104.94126086956521</v>
       </c>
-      <c r="O154" s="24">
+      <c r="O154" s="20">
         <v>14875.004999999999</v>
       </c>
-      <c r="P154" s="24">
+      <c r="P154" s="20">
         <v>14838.782608695652</v>
       </c>
     </row>
@@ -14822,10 +14910,10 @@
       <c r="M155" s="6">
         <v>128.09490909090908</v>
       </c>
-      <c r="O155" s="24">
+      <c r="O155" s="20">
         <v>15247</v>
       </c>
-      <c r="P155" s="24">
+      <c r="P155" s="20">
         <v>14985.863636363636</v>
       </c>
     </row>
@@ -14876,10 +14964,10 @@
       <c r="M156" s="6">
         <v>153.26790476190476</v>
       </c>
-      <c r="O156" s="24">
+      <c r="O156" s="20">
         <v>15542</v>
       </c>
-      <c r="P156" s="24">
+      <c r="P156" s="20">
         <v>15435.904761904761</v>
       </c>
     </row>
@@ -14930,10 +15018,10 @@
       <c r="M157" s="6">
         <v>113.66349999999998</v>
       </c>
-      <c r="O157" s="24">
+      <c r="O157" s="20">
         <v>15737</v>
       </c>
-      <c r="P157" s="24">
+      <c r="P157" s="20">
         <v>15663.954545454546</v>
       </c>
     </row>
@@ -14984,10 +15072,10 @@
       <c r="M158" s="6">
         <v>98.854909090909118</v>
       </c>
-      <c r="O158" s="24">
+      <c r="O158" s="20">
         <v>15731</v>
       </c>
-      <c r="P158" s="24">
+      <c r="P158" s="20">
         <v>15600.363636363636</v>
       </c>
     </row>
@@ -15038,10 +15126,10 @@
       <c r="M159" s="6">
         <v>90.202136363636342</v>
       </c>
-      <c r="O159" s="24">
+      <c r="O159" s="20">
         <v>14979</v>
       </c>
-      <c r="P159" s="24">
+      <c r="P159" s="20">
         <v>15245.954545454546</v>
       </c>
     </row>
@@ -15092,10 +15180,10 @@
       <c r="M160" s="6">
         <v>90.466800000000006</v>
       </c>
-      <c r="O160" s="24">
+      <c r="O160" s="20">
         <v>15274</v>
       </c>
-      <c r="P160" s="24">
+      <c r="P160" s="20">
         <v>15134.05</v>
       </c>
     </row>
@@ -15146,10 +15234,10 @@
       <c r="M161" s="6">
         <v>102.52921739130434</v>
       </c>
-      <c r="O161" s="24">
+      <c r="O161" s="20">
         <v>15062</v>
       </c>
-      <c r="P161" s="24">
+      <c r="P161" s="20">
         <v>15283.217391304348</v>
       </c>
     </row>
@@ -15200,10 +15288,10 @@
       <c r="M162" s="6">
         <v>93.353300000000004</v>
       </c>
-      <c r="O162" s="24">
+      <c r="O162" s="20">
         <v>14751</v>
       </c>
-      <c r="P162" s="24">
+      <c r="P162" s="20">
         <v>14840.15</v>
       </c>
     </row>
@@ -15254,10 +15342,10 @@
       <c r="M163" s="6">
         <v>94.360217391304346</v>
       </c>
-      <c r="O163" s="24">
+      <c r="O163" s="20">
         <v>14969</v>
       </c>
-      <c r="P163" s="24">
+      <c r="P163" s="20">
         <v>14819.434782608696</v>
       </c>
     </row>
@@ -15308,10 +15396,10 @@
       <c r="M164" s="6">
         <v>85.735772727272717</v>
       </c>
-      <c r="O164" s="24">
+      <c r="O164" s="20">
         <v>15026</v>
       </c>
-      <c r="P164" s="24">
+      <c r="P164" s="20">
         <v>14941.59090909091</v>
       </c>
     </row>
@@ -15362,10 +15450,10 @@
       <c r="M165" s="6">
         <v>81.811285714285717</v>
       </c>
-      <c r="O165" s="24">
+      <c r="O165" s="20">
         <v>15083</v>
       </c>
-      <c r="P165" s="24">
+      <c r="P165" s="20">
         <v>15036.619047619048</v>
       </c>
     </row>
@@ -15416,10 +15504,10 @@
       <c r="M166" s="6">
         <v>83.005304347826069</v>
       </c>
-      <c r="O166" s="24">
+      <c r="O166" s="20">
         <v>15239</v>
       </c>
-      <c r="P166" s="24">
+      <c r="P166" s="20">
         <v>15245.217391304348</v>
       </c>
     </row>
@@ -15470,10 +15558,10 @@
       <c r="M167" s="6">
         <v>83.577380952380949</v>
       </c>
-      <c r="O167" s="24">
+      <c r="O167" s="20">
         <v>15526</v>
       </c>
-      <c r="P167" s="24">
+      <c r="P167" s="20">
         <v>15366.666666666666</v>
       </c>
     </row>
@@ -15524,10 +15612,10 @@
       <c r="M168" s="6">
         <v>98.448727272727268</v>
       </c>
-      <c r="O168" s="24">
+      <c r="O168" s="20">
         <v>15916</v>
       </c>
-      <c r="P168" s="24">
+      <c r="P168" s="20">
         <v>15754.681818181818</v>
       </c>
     </row>
@@ -15578,10 +15666,10 @@
       <c r="M169" s="6">
         <v>80.58750000000002</v>
       </c>
-      <c r="O169" s="24">
+      <c r="O169" s="20">
         <v>15384</v>
       </c>
-      <c r="P169" s="24">
+      <c r="P169" s="20">
         <v>15594.136363636364</v>
       </c>
     </row>
@@ -15632,10 +15720,10 @@
       <c r="M170" s="6">
         <v>72.753285714285695</v>
       </c>
-      <c r="O170" s="24">
+      <c r="O170" s="20">
         <v>15416</v>
       </c>
-      <c r="P170" s="24">
+      <c r="P170" s="20">
         <v>15504.476190476191</v>
       </c>
     </row>
@@ -15686,10 +15774,10 @@
       <c r="M171" s="6">
         <v>74.998478260869575</v>
       </c>
-      <c r="O171" s="24">
+      <c r="O171" s="20">
         <v>15796</v>
       </c>
-      <c r="P171" s="24">
+      <c r="P171" s="20">
         <v>15612.04347826087</v>
       </c>
     </row>
@@ -15740,10 +15828,10 @@
       <c r="M172" s="6">
         <v>72.257095238095232</v>
       </c>
-      <c r="O172" s="24">
+      <c r="O172" s="20">
         <v>15673</v>
       </c>
-      <c r="P172" s="24">
+      <c r="P172" s="20">
         <v>15646.095238095239</v>
       </c>
     </row>
@@ -15794,10 +15882,10 @@
       <c r="M173" s="6">
         <v>70.242666666666665</v>
       </c>
-      <c r="O173" s="24">
+      <c r="O173" s="20">
         <v>15853</v>
       </c>
-      <c r="P173" s="24">
+      <c r="P173" s="20">
         <v>15704.761904761905</v>
       </c>
     </row>
@@ -15848,10 +15936,10 @@
       <c r="M174" s="6">
         <v>76.358227272727262</v>
       </c>
-      <c r="O174" s="24">
+      <c r="O174" s="20">
         <v>16249</v>
       </c>
-      <c r="P174" s="24">
+      <c r="P174" s="20">
         <v>16039.181818181818</v>
       </c>
     </row>
@@ -15902,10 +15990,10 @@
       <c r="M175" s="6">
         <v>71.828565217391315</v>
       </c>
-      <c r="O175" s="24">
+      <c r="O175" s="20">
         <v>16253</v>
       </c>
-      <c r="P175" s="24">
+      <c r="P175" s="20">
         <v>16069.739130434782</v>
       </c>
     </row>
@@ -15956,10 +16044,10 @@
       <c r="M176" s="6">
         <v>75.124750000000006</v>
       </c>
-      <c r="O176" s="24">
+      <c r="O176" s="20">
         <v>16421</v>
       </c>
-      <c r="P176" s="24">
+      <c r="P176" s="20">
         <v>16335.85</v>
       </c>
     </row>
@@ -16010,10 +16098,10 @@
       <c r="M177" s="6">
         <v>74.01926086956523</v>
       </c>
-      <c r="O177" s="24">
+      <c r="O177" s="20">
         <v>16320</v>
       </c>
-      <c r="P177" s="24">
+      <c r="P177" s="20">
         <v>16243.260869565218</v>
       </c>
     </row>
@@ -16064,10 +16152,10 @@
       <c r="M178" s="6">
         <v>73.582590909090911</v>
       </c>
-      <c r="O178" s="24">
+      <c r="O178" s="20">
         <v>15409</v>
       </c>
-      <c r="P178" s="24">
+      <c r="P178" s="20">
         <v>15739.727272727272</v>
       </c>
     </row>
@@ -16118,10 +16206,10 @@
       <c r="M179" s="6">
         <v>69.288714285714278</v>
       </c>
-      <c r="O179" s="24">
+      <c r="O179" s="20">
         <v>15138</v>
       </c>
-      <c r="P179" s="24">
+      <c r="P179" s="20">
         <v>15323.904761904761</v>
       </c>
     </row>
@@ -16172,10 +16260,10 @@
       <c r="M180" s="6">
         <v>68.92404347826087</v>
       </c>
-      <c r="O180" s="24">
+      <c r="O180" s="20">
         <v>15732</v>
       </c>
-      <c r="P180" s="24">
+      <c r="P180" s="20">
         <v>15563.217391304348</v>
       </c>
     </row>
@@ -16226,10 +16314,10 @@
       <c r="M181" s="6">
         <v>72.635238095238094</v>
       </c>
-      <c r="O181" s="24">
+      <c r="O181" s="20">
         <v>15864</v>
       </c>
-      <c r="P181" s="24">
+      <c r="P181" s="20">
         <v>15818</v>
       </c>
     </row>
@@ -16280,10 +16368,10 @@
       <c r="M182" s="6">
         <v>74.619590909090917</v>
       </c>
-      <c r="O182" s="24">
+      <c r="O182" s="20">
         <v>16162</v>
       </c>
-      <c r="P182" s="24">
+      <c r="P182" s="20">
         <v>16041.681818181818</v>
       </c>
     </row>
@@ -16334,10 +16422,10 @@
       <c r="M183" s="6">
         <v>77.286695652173904</v>
       </c>
-      <c r="O183" s="24">
+      <c r="O183" s="20">
         <v>16259</v>
       </c>
-      <c r="P183" s="24">
+      <c r="P183" s="20">
         <v>16238.695652173914</v>
       </c>
     </row>
@@ -16388,10 +16476,10 @@
       <c r="M184" s="6">
         <v>73.931150000000002</v>
       </c>
-      <c r="O184" s="24">
+      <c r="O184" s="20">
         <v>16430.994999999999</v>
       </c>
-      <c r="P184" s="24">
+      <c r="P184" s="20">
         <v>16342.35</v>
       </c>
     </row>
@@ -16442,10 +16530,10 @@
       <c r="M185" s="6">
         <v>84.90695238095239</v>
       </c>
-      <c r="O185" s="24">
+      <c r="O185" s="20">
         <v>16588</v>
       </c>
-      <c r="P185" s="24">
+      <c r="P185" s="20">
         <v>16455.380952380954</v>
       </c>
     </row>
@@ -16496,10 +16584,10 @@
       <c r="M186" s="6">
         <v>107.06404545454544</v>
       </c>
-      <c r="O186" s="24">
+      <c r="O186" s="20">
         <v>16787</v>
       </c>
-      <c r="P186" s="24">
+      <c r="P186" s="20">
         <v>16756.045454545456</v>
       </c>
     </row>
@@ -16550,10 +16638,10 @@
       <c r="M187" s="6">
         <v>86.467818181818174</v>
       </c>
-      <c r="O187" s="24">
+      <c r="O187" s="20">
         <v>16255</v>
       </c>
-      <c r="P187" s="24">
+      <c r="P187" s="20">
         <v>16417.136363636364</v>
       </c>
     </row>
@@ -16604,10 +16692,10 @@
       <c r="M188" s="6">
         <v>78.105571428571452</v>
       </c>
-      <c r="O188" s="24">
+      <c r="O188" s="20">
         <v>16233</v>
       </c>
-      <c r="P188" s="24">
+      <c r="P188" s="20">
         <v>16291.142857142857</v>
       </c>
     </row>
@@ -16658,10 +16746,10 @@
       <c r="M189" s="6">
         <v>73.85108695652174</v>
       </c>
-      <c r="O189" s="24">
+      <c r="O189" s="20">
         <v>16387.005000000001</v>
       </c>
-      <c r="P189" s="24">
+      <c r="P189" s="20">
         <v>16280.130434782608</v>
       </c>
     </row>
@@ -16712,10 +16800,10 @@
       <c r="M190" s="6">
         <v>70.2942380952381</v>
       </c>
-      <c r="O190" s="24">
+      <c r="O190" s="20">
         <v>16356</v>
       </c>
-      <c r="P190" s="24">
+      <c r="P190" s="20">
         <v>16299.238095238095</v>
       </c>
     </row>
@@ -16766,10 +16854,10 @@
       <c r="M191" s="6">
         <v>73.98981818181818</v>
       </c>
-      <c r="O191" s="24">
+      <c r="O191" s="20">
         <v>16680</v>
       </c>
-      <c r="P191" s="24">
+      <c r="P191" s="20">
         <v>16514.136363636364</v>
       </c>
     </row>
@@ -16821,10 +16909,10 @@
       <c r="M192" s="6">
         <v>79.221956521739116</v>
       </c>
-      <c r="O192" s="24">
+      <c r="O192" s="20">
         <v>16640</v>
       </c>
-      <c r="P192" s="24">
+      <c r="P192" s="20">
         <v>16583.130434782608</v>
       </c>
     </row>
@@ -16875,10 +16963,10 @@
       <c r="M193" s="6">
         <v>75.448200000000014</v>
       </c>
-      <c r="O193" s="24">
+      <c r="O193" s="20">
         <v>16644</v>
       </c>
-      <c r="P193" s="24">
+      <c r="P193" s="20">
         <v>16692.45</v>
       </c>
     </row>
@@ -16929,10 +17017,10 @@
       <c r="M194" s="6">
         <v>71.1198695652174</v>
       </c>
-      <c r="O194" s="24">
+      <c r="O194" s="20">
         <v>16782</v>
       </c>
-      <c r="P194" s="24">
+      <c r="P194" s="20">
         <v>16702.217391304348</v>
       </c>
     </row>
@@ -16956,15 +17044,15 @@
       </c>
       <c r="F195" s="5">
         <f>Sheet3!D211/Sheet3!C211</f>
-        <v>0.39399006824013183</v>
+        <v>0.39399006826234167</v>
       </c>
       <c r="G195" s="5">
         <f>Sheet3!E211/Sheet3!F211</f>
-        <v>0.92702447247400843</v>
+        <v>0.92702447246165531</v>
       </c>
       <c r="H195" s="6">
         <f t="shared" si="10"/>
-        <v>0.42500503486026187</v>
+        <v>0.4250050348898835</v>
       </c>
       <c r="I195" s="6">
         <f>LN(Sheet3!B211)</f>
@@ -16983,10 +17071,10 @@
       <c r="M195" s="6">
         <v>72.201045454545451</v>
       </c>
-      <c r="O195" s="24">
+      <c r="O195" s="20">
         <v>16786</v>
       </c>
-      <c r="P195" s="24">
+      <c r="P195" s="20">
         <v>16814.863636363636</v>
       </c>
     </row>
@@ -17010,15 +17098,15 @@
       </c>
       <c r="F196" s="5">
         <f>Sheet3!D212/Sheet3!C212</f>
-        <v>0.42134055259190589</v>
+        <v>0.42134055259983449</v>
       </c>
       <c r="G196" s="5">
         <f>Sheet3!E212/Sheet3!F212</f>
-        <v>0.94223827383482428</v>
+        <v>0.9422382737979208</v>
       </c>
       <c r="H196" s="6">
-        <f t="shared" ref="H196:H199" si="14">F196/G196</f>
-        <v>0.44716985532447973</v>
+        <f t="shared" ref="H196:H197" si="14">F196/G196</f>
+        <v>0.44716985535040815</v>
       </c>
       <c r="I196" s="6">
         <f>LN(Sheet3!B212)</f>
@@ -17037,10 +17125,10 @@
       <c r="M196" s="6">
         <v>80.089349999999996</v>
       </c>
-      <c r="O196" s="24">
+      <c r="O196" s="20">
         <v>16758</v>
       </c>
-      <c r="P196" s="24">
+      <c r="P196" s="20">
         <v>16815.349999999999</v>
       </c>
     </row>
@@ -17064,15 +17152,15 @@
       </c>
       <c r="F197" s="5">
         <f>Sheet3!D213/Sheet3!C213</f>
-        <v>0.41799486229820598</v>
+        <v>0.41799486233442684</v>
       </c>
       <c r="G197" s="5">
         <f>Sheet3!E213/Sheet3!F213</f>
-        <v>1.1021852731987214</v>
+        <v>1.1021862589413383</v>
       </c>
       <c r="H197" s="6">
         <f t="shared" si="14"/>
-        <v>0.37924192280769342</v>
+        <v>0.37924158366473865</v>
       </c>
       <c r="I197" s="6">
         <f>LN(Sheet3!B213)</f>
@@ -17091,10 +17179,10 @@
       <c r="M197" s="6">
         <v>93.77709090909093</v>
       </c>
-      <c r="O197" s="24">
+      <c r="O197" s="20">
         <v>16993</v>
       </c>
-      <c r="P197" s="24">
+      <c r="P197" s="20">
         <v>16935.045454545456</v>
       </c>
     </row>
@@ -17118,15 +17206,15 @@
       </c>
       <c r="F198" s="5">
         <f>Sheet3!D214/Sheet3!C214</f>
-        <v>0.39246379999530162</v>
+        <v>0.47080132286428161</v>
       </c>
       <c r="G198" s="5">
         <f>Sheet3!E214/Sheet3!F214</f>
-        <v>1.0482968549383866</v>
+        <v>1.0469816529278275</v>
       </c>
       <c r="H198" s="6">
         <f>F198/G198</f>
-        <v>0.37438231179122305</v>
+        <v>0.44967485490095382</v>
       </c>
       <c r="I198" s="6">
         <f>LN(Sheet3!B214)</f>
@@ -17145,10 +17233,10 @@
       <c r="M198" s="6">
         <v>88.659409090909108</v>
       </c>
-      <c r="O198" s="24">
+      <c r="O198" s="20">
         <v>17324</v>
       </c>
-      <c r="P198" s="24">
+      <c r="P198" s="20">
         <v>17138.590909090908</v>
       </c>
     </row>
@@ -17160,10 +17248,10 @@
         <f t="shared" si="12"/>
         <v>17789</v>
       </c>
-      <c r="C199" s="21">
+      <c r="C199" s="19">
         <v>2.59</v>
       </c>
-      <c r="D199" s="21">
+      <c r="D199" s="19">
         <v>2.9</v>
       </c>
       <c r="E199" s="8">
@@ -17172,15 +17260,15 @@
       </c>
       <c r="F199" s="5">
         <f>Sheet3!D215/Sheet3!C215</f>
-        <v>0.42520887723573753</v>
+        <v>0.42408491974896417</v>
       </c>
       <c r="G199" s="5">
         <f>Sheet3!E215/Sheet3!F215</f>
-        <v>0.90363046987703999</v>
+        <v>0.90346575933060791</v>
       </c>
       <c r="H199" s="6">
         <f>F199/G199</f>
-        <v>0.47055615255381672</v>
+        <v>0.46939788848575226</v>
       </c>
       <c r="I199" s="6">
         <f>LN(Sheet3!B215)</f>
@@ -17199,10 +17287,10 @@
       <c r="M199" s="6">
         <v>88.392947368421048</v>
       </c>
-      <c r="O199" s="24">
+      <c r="O199" s="20">
         <v>17789</v>
       </c>
-      <c r="P199" s="24">
+      <c r="P199" s="20">
         <v>17542.315789473683</v>
       </c>
     </row>
@@ -17214,7 +17302,7 @@
         <f t="shared" si="12"/>
         <v>17962</v>
       </c>
-      <c r="C200" s="26">
+      <c r="C200" s="21">
         <v>2.76</v>
       </c>
       <c r="D200" s="12">
@@ -17226,15 +17314,15 @@
       </c>
       <c r="F200" s="5">
         <f>Sheet3!D216/Sheet3!C216</f>
-        <v>0.4476880960265161</v>
+        <v>0.4504062402856282</v>
       </c>
       <c r="G200" s="5">
         <f>Sheet3!E216/Sheet3!F216</f>
-        <v>0.97010564631954999</v>
+        <v>0.96480833123137733</v>
       </c>
       <c r="H200" s="14">
         <f>F200/G200</f>
-        <v>0.46148385768599987</v>
+        <v>0.46683494089523275</v>
       </c>
       <c r="I200" s="14">
         <f>LN(Sheet3!B216)</f>
@@ -17253,10 +17341,10 @@
       <c r="M200" s="6">
         <v>89.87</v>
       </c>
-      <c r="O200" s="24">
+      <c r="O200" s="20">
         <v>17962</v>
       </c>
-      <c r="P200" s="24">
+      <c r="P200" s="20">
         <v>17905.5</v>
       </c>
     </row>
@@ -17321,7 +17409,7 @@
         <f t="shared" si="0"/>
         <v>Import: cif</v>
       </c>
-      <c r="O1" s="18" t="s">
+      <c r="O1" s="17" t="s">
         <v>41</v>
       </c>
     </row>
@@ -21402,7 +21490,7 @@
         <f t="shared" ref="N203" si="5">F203/F191*100-100</f>
         <v>4.1376899101669835</v>
       </c>
-      <c r="O203" s="17">
+      <c r="O203" s="16">
         <f t="shared" ref="O203:O212" si="6">D203-F203</f>
         <v>4301.500759999999</v>
       </c>
@@ -21446,7 +21534,7 @@
         <f t="shared" ref="N204:N213" si="11">F204/F192*100-100</f>
         <v>4.2809177087114136</v>
       </c>
-      <c r="O204" s="17">
+      <c r="O204" s="16">
         <f t="shared" si="6"/>
         <v>4103.5</v>
       </c>
@@ -21490,7 +21578,7 @@
         <f t="shared" si="11"/>
         <v>-5.8574370765916086</v>
       </c>
-      <c r="O205" s="17">
+      <c r="O205" s="16">
         <f t="shared" si="6"/>
         <v>4173.5</v>
       </c>
@@ -21534,7 +21622,7 @@
         <f t="shared" si="11"/>
         <v>-6.5643296149092976</v>
       </c>
-      <c r="O206" s="17">
+      <c r="O206" s="16">
         <f t="shared" si="6"/>
         <v>5488</v>
       </c>
@@ -21578,7 +21666,7 @@
         <f t="shared" si="11"/>
         <v>7.1743149321215469</v>
       </c>
-      <c r="O207" s="17">
+      <c r="O207" s="16">
         <f t="shared" si="6"/>
         <v>4343.7999999999993</v>
       </c>
@@ -21622,7 +21710,7 @@
         <f t="shared" si="11"/>
         <v>-1.1526034265854577</v>
       </c>
-      <c r="O208" s="17">
+      <c r="O208" s="16">
         <f t="shared" si="6"/>
         <v>2393.2000000000007</v>
       </c>
@@ -21666,7 +21754,7 @@
         <f t="shared" si="11"/>
         <v>0.4561837512669058</v>
       </c>
-      <c r="O209" s="17">
+      <c r="O209" s="16">
         <f t="shared" si="6"/>
         <v>2662.3119699999988</v>
       </c>
@@ -21710,7 +21798,7 @@
         <f t="shared" si="11"/>
         <v>10.807698496278789</v>
       </c>
-      <c r="O210" s="17">
+      <c r="O210" s="16">
         <f t="shared" si="6"/>
         <v>2512.744999999999</v>
       </c>
@@ -21722,17 +21810,17 @@
       <c r="B211" s="5">
         <v>2151388.9890000001</v>
       </c>
-      <c r="C211" s="5">
-        <v>56234.158640000001</v>
-      </c>
-      <c r="D211" s="5">
+      <c r="C211" s="19">
+        <v>56234.158636829998</v>
+      </c>
+      <c r="D211" s="19">
         <v>22155.7</v>
       </c>
-      <c r="E211" s="5">
-        <v>19654.170419999999</v>
-      </c>
-      <c r="F211" s="5">
-        <v>21201.350129999999</v>
+      <c r="E211" s="19">
+        <v>19654.17041603</v>
+      </c>
+      <c r="F211" s="19">
+        <v>21201.350126000001</v>
       </c>
       <c r="J211" s="5">
         <f t="shared" si="7"/>
@@ -21740,7 +21828,7 @@
       </c>
       <c r="K211" s="5">
         <f t="shared" si="8"/>
-        <v>1.77767188454105</v>
+        <v>1.7776718788036874</v>
       </c>
       <c r="L211" s="5">
         <f t="shared" si="9"/>
@@ -21748,15 +21836,15 @@
       </c>
       <c r="M211" s="5">
         <f t="shared" si="10"/>
-        <v>25.510527685031008</v>
+        <v>25.5105276596788</v>
       </c>
       <c r="N211" s="5">
         <f t="shared" si="11"/>
-        <v>18.206122372537365</v>
-      </c>
-      <c r="O211" s="17">
+        <v>18.206122350235759</v>
+      </c>
+      <c r="O211" s="16">
         <f t="shared" si="6"/>
-        <v>954.34987000000183</v>
+        <v>954.34987399999955</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.75">
@@ -21766,17 +21854,17 @@
       <c r="B212" s="5">
         <v>2093675.1310000001</v>
       </c>
-      <c r="C212" s="5">
-        <v>52610.174509999997</v>
-      </c>
-      <c r="D212" s="5">
+      <c r="C212" s="19">
+        <v>52610.174509010001</v>
+      </c>
+      <c r="D212" s="19">
         <v>22166.799999999999</v>
       </c>
-      <c r="E212" s="5">
-        <v>19686.70161</v>
-      </c>
-      <c r="F212" s="5">
-        <v>20893.549070000001</v>
+      <c r="E212" s="19">
+        <v>19686.701605459999</v>
+      </c>
+      <c r="F212" s="19">
+        <v>20893.549066</v>
       </c>
       <c r="J212" s="5">
         <f t="shared" si="7"/>
@@ -21784,7 +21872,7 @@
       </c>
       <c r="K212" s="5">
         <f t="shared" si="8"/>
-        <v>-7.0800896412657579</v>
+        <v>-7.0800896430143041</v>
       </c>
       <c r="L212" s="5">
         <f t="shared" si="9"/>
@@ -21792,15 +21880,15 @@
       </c>
       <c r="M212" s="5">
         <f t="shared" si="10"/>
-        <v>-2.2770381949430458</v>
+        <v>-2.2770382174792019</v>
       </c>
       <c r="N212" s="5">
         <f t="shared" si="11"/>
-        <v>10.84699195388599</v>
-      </c>
-      <c r="O212" s="17">
+        <v>10.846991932664693</v>
+      </c>
+      <c r="O212" s="16">
         <f t="shared" si="6"/>
-        <v>1273.2509299999983</v>
+        <v>1273.2509339999997</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.75">
@@ -21810,17 +21898,17 @@
       <c r="B213" s="5">
         <v>2102220.5690000001</v>
       </c>
-      <c r="C213" s="5">
-        <v>53892.528429999998</v>
-      </c>
-      <c r="D213" s="5">
+      <c r="C213" s="19">
+        <v>53892.528425329998</v>
+      </c>
+      <c r="D213" s="19">
         <v>22526.799999999999</v>
       </c>
-      <c r="E213" s="5">
-        <v>21168.349920000001</v>
-      </c>
-      <c r="F213" s="5">
-        <v>19205.8</v>
+      <c r="E213" s="19">
+        <v>21168.349918619999</v>
+      </c>
+      <c r="F213" s="19">
+        <v>19205.782822000001</v>
       </c>
       <c r="J213" s="5">
         <f t="shared" si="7"/>
@@ -21828,7 +21916,7 @@
       </c>
       <c r="K213" s="5">
         <f t="shared" si="8"/>
-        <v>-6.5146905853170978</v>
+        <v>-6.5146905934179671</v>
       </c>
       <c r="L213" s="5">
         <f t="shared" si="9"/>
@@ -21836,15 +21924,15 @@
       </c>
       <c r="M213" s="5">
         <f t="shared" si="10"/>
-        <v>11.398231505791273</v>
+        <v>11.398231498529015</v>
       </c>
       <c r="N213" s="5">
         <f t="shared" si="11"/>
-        <v>1.510689343082845</v>
-      </c>
-      <c r="O213" s="17">
+        <v>1.5105985501649997</v>
+      </c>
+      <c r="O213" s="16">
         <f>D213-F213</f>
-        <v>3321</v>
+        <v>3321.0171779999982</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.75">
@@ -21855,32 +21943,24 @@
         <v>2052500</v>
       </c>
       <c r="C214" s="19">
-        <f>C202*1.21</f>
-        <v>64471.678662599996</v>
-      </c>
-      <c r="D214" s="15">
+        <v>53744.114069310002</v>
+      </c>
+      <c r="D214" s="19">
         <v>25302.799999999999</v>
       </c>
       <c r="E214" s="19">
-        <f>E202*1.426</f>
-        <v>26431.44241136</v>
-      </c>
-      <c r="F214" s="15">
-        <v>25213.7</v>
-      </c>
-      <c r="G214" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="H214" s="16" t="s">
-        <v>39</v>
+        <v>26398.289369419999</v>
+      </c>
+      <c r="F214" s="19">
+        <v>25213.707705000001</v>
       </c>
       <c r="J214" s="5">
         <f>B214/B202*100-100</f>
         <v>3.6577718194443065</v>
       </c>
       <c r="K214" s="5">
-        <f t="shared" ref="K214:N214" si="12">C214/C202*100-100</f>
-        <v>21</v>
+        <f t="shared" ref="K214:N217" si="12">C214/C202*100-100</f>
+        <v>0.86658106761720433</v>
       </c>
       <c r="L214" s="5">
         <f t="shared" si="12"/>
@@ -21888,69 +21968,63 @@
       </c>
       <c r="M214" s="5">
         <f t="shared" si="12"/>
-        <v>42.599999999999994</v>
+        <v>42.421136368304587</v>
       </c>
       <c r="N214" s="5">
         <f t="shared" si="12"/>
-        <v>22.485705714305553</v>
-      </c>
-      <c r="O214" s="17">
+        <v>22.485743144447198</v>
+      </c>
+      <c r="O214" s="16">
         <f>D214-F214</f>
-        <v>89.099999999998545</v>
+        <v>89.092294999998558</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A215" s="9">
         <v>46143</v>
       </c>
-      <c r="B215" s="5">
+      <c r="B215" s="12">
         <f>B203*(1+J215%)</f>
         <v>2057097.1165200002</v>
       </c>
-      <c r="C215" s="22">
-        <f>C203*(1+K215%)</f>
-        <v>54569.486508420006</v>
-      </c>
-      <c r="D215" s="22">
-        <f t="shared" ref="D215:E215" si="13">D203*(1+L215%)</f>
-        <v>23203.430089575999</v>
-      </c>
-      <c r="E215" s="22">
-        <f t="shared" si="13"/>
-        <v>22422.239929380001</v>
-      </c>
-      <c r="F215" s="22">
-        <f>F203*(1+N215%)</f>
-        <v>24813.505826592002</v>
-      </c>
-      <c r="G215" s="20" t="s">
-        <v>38</v>
-      </c>
+      <c r="C215" s="19">
+        <v>54714.277540770003</v>
+      </c>
+      <c r="D215" s="19">
+        <v>23203.5</v>
+      </c>
+      <c r="E215" s="19">
+        <v>22418.37203101</v>
+      </c>
+      <c r="F215" s="19">
+        <v>24813.748390000001</v>
+      </c>
+      <c r="G215" s="18"/>
       <c r="J215" s="5">
         <v>5.2</v>
       </c>
-      <c r="K215" s="22">
-        <v>-7.7</v>
-      </c>
-      <c r="L215" s="15">
-        <v>-5.73</v>
-      </c>
-      <c r="M215" s="22">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="N215" s="15">
-        <v>22.16</v>
-      </c>
-      <c r="O215" s="23">
-        <f t="shared" ref="O215" si="14">D215-F215</f>
-        <v>-1610.0757370160027</v>
-      </c>
-      <c r="P215" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q215" s="16" t="s">
-        <v>39</v>
-      </c>
+      <c r="K215" s="5">
+        <f t="shared" si="12"/>
+        <v>-7.4550973421044944</v>
+      </c>
+      <c r="L215" s="5">
+        <f t="shared" si="12"/>
+        <v>-5.7297159706282628</v>
+      </c>
+      <c r="M215" s="5">
+        <f t="shared" si="12"/>
+        <v>10.18099019537226</v>
+      </c>
+      <c r="N215" s="5">
+        <f t="shared" si="12"/>
+        <v>22.161194170067233</v>
+      </c>
+      <c r="O215" s="16">
+        <f t="shared" ref="O215:O216" si="13">D215-F215</f>
+        <v>-1610.2483900000007</v>
+      </c>
+      <c r="P215" s="18"/>
+      <c r="Q215" s="15"/>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A216" s="9">
@@ -21960,67 +22034,77 @@
         <f>B204*(1+J216%)</f>
         <v>2076404.0528398708</v>
       </c>
-      <c r="C216" s="27">
-        <f>C204*(1+K216%)</f>
-        <v>56433.367838540005</v>
-      </c>
-      <c r="D216" s="27">
-        <f>D204*(1+L216%)</f>
-        <v>25264.547000000002</v>
-      </c>
-      <c r="E216" s="27">
-        <f>E204*(1+M216%)</f>
-        <v>25356.830926320003</v>
-      </c>
-      <c r="F216" s="27">
-        <f>F204*(1+N216%)</f>
-        <v>26138.216</v>
-      </c>
-      <c r="G216" s="20" t="s">
-        <v>38</v>
-      </c>
+      <c r="C216" s="19">
+        <v>56523.861622910001</v>
+      </c>
+      <c r="D216" s="19">
+        <v>25458.7</v>
+      </c>
+      <c r="E216" s="19">
+        <v>24997.412015540001</v>
+      </c>
+      <c r="F216" s="19">
+        <v>25909.200000000001</v>
+      </c>
+      <c r="G216" s="18"/>
       <c r="J216" s="12">
         <f>_xlfn.FORECAST.LINEAR(J215,J204:J215,J203:J214)</f>
         <v>5.6756715110322711</v>
       </c>
-      <c r="K216" s="27">
-        <v>7.8</v>
-      </c>
-      <c r="L216" s="27">
-        <v>7.8</v>
-      </c>
-      <c r="M216" s="27">
-        <v>24.2</v>
-      </c>
-      <c r="N216" s="27">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="O216" s="12"/>
-      <c r="P216" s="20" t="s">
+      <c r="K216" s="5">
+        <f t="shared" si="12"/>
+        <v>7.9728627995939689</v>
+      </c>
+      <c r="L216" s="5">
+        <f t="shared" si="12"/>
+        <v>8.628421479316458</v>
+      </c>
+      <c r="M216" s="5">
+        <f t="shared" si="12"/>
+        <v>22.439534394160404</v>
+      </c>
+      <c r="N216" s="5">
+        <f t="shared" si="12"/>
+        <v>34.015414058863087</v>
+      </c>
+      <c r="O216" s="16">
+        <f t="shared" si="13"/>
+        <v>-450.5</v>
+      </c>
+      <c r="P216" s="18" t="s">
         <v>38</v>
+      </c>
+      <c r="Q216" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="217" spans="1:17" x14ac:dyDescent="0.75">
       <c r="B217" s="12"/>
+      <c r="G217" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="H217" s="15" t="s">
+        <v>39</v>
+      </c>
       <c r="J217" s="12">
         <f>_xlfn.FORECAST.LINEAR(J216,J205:J216,J204:J215)</f>
         <v>6.1223116507551287</v>
       </c>
       <c r="K217" s="12">
-        <f t="shared" ref="K216:N217" si="15">_xlfn.FORECAST.LINEAR(K216,K205:K216,K204:K215)</f>
-        <v>-1.7663752987401886</v>
+        <f t="shared" ref="K217:N217" si="14">_xlfn.FORECAST.LINEAR(K216,K205:K216,K204:K215)</f>
+        <v>-1.5571138801144961</v>
       </c>
       <c r="L217" s="12">
-        <f t="shared" si="15"/>
-        <v>3.4582367498823601</v>
+        <f t="shared" si="14"/>
+        <v>3.1638925862450153</v>
       </c>
       <c r="M217" s="12">
-        <f t="shared" si="15"/>
-        <v>12.087529966289031</v>
+        <f t="shared" si="14"/>
+        <v>11.807078045247842</v>
       </c>
       <c r="N217" s="12">
-        <f t="shared" si="15"/>
-        <v>31.602084072676309</v>
+        <f t="shared" si="14"/>
+        <v>30.147253793494126</v>
       </c>
       <c r="P217" s="13" t="s">
         <v>42</v>
@@ -22028,6 +22112,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22073,7 +22158,7 @@
       </c>
       <c r="D2" s="11">
         <f>Sheet2!H198</f>
-        <v>0.37438231179122305</v>
+        <v>0.44967485490095382</v>
       </c>
       <c r="E2" s="11">
         <f>Sheet2!I198</f>
@@ -22102,7 +22187,7 @@
       </c>
       <c r="D3" s="11">
         <f>Sheet2!H199</f>
-        <v>0.47055615255381672</v>
+        <v>0.46939788848575226</v>
       </c>
       <c r="E3" s="11">
         <f>Sheet2!I199</f>

--- a/data_mod_rupiah.xlsx
+++ b/data_mod_rupiah.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfan\GitHub\beer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alfan\Documents\0. Gawean\0. DEN\22. XR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CC6220-3622-46EA-AAB7-7E78992743B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD31B983-83AC-4937-8723-71DAAC377996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" activeTab="2" xr2:uid="{136FD5EA-69F6-4D36-BF21-61416DD08A06}"/>
+    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="11460" xr2:uid="{136FD5EA-69F6-4D36-BF21-61416DD08A06}"/>
   </bookViews>
   <sheets>
     <sheet name="data_clean" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,8 @@
     <author>tc={4E777C20-B01C-46C1-B7E6-752D407CE2FF}</author>
     <author>tc={0B667D67-D354-423D-8013-6CAC4AE3F5B2}</author>
     <author>tc={C1984FB3-39AE-427D-8EF3-64A0FBB19F58}</author>
-    <author>tc={CD67C6B1-A286-4708-AD00-4F70ABEAB931}</author>
+    <author>tc={A0063725-D041-46FA-8092-72645EA654D4}</author>
+    <author>tc={E6F2F672-2090-4050-9A85-27C3181E2283}</author>
   </authors>
   <commentList>
     <comment ref="B1" authorId="0" shapeId="0" xr:uid="{4E777C20-B01C-46C1-B7E6-752D407CE2FF}">
@@ -74,12 +75,20 @@
     Average, Bloomberg</t>
       </text>
     </comment>
-    <comment ref="D200" authorId="3" shapeId="0" xr:uid="{CD67C6B1-A286-4708-AD00-4F70ABEAB931}">
+    <comment ref="C203" authorId="3" shapeId="0" xr:uid="{A0063725-D041-46FA-8092-72645EA654D4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
-    Forecast Trading Economics</t>
+    Trading Economics consensus</t>
+      </text>
+    </comment>
+    <comment ref="D203" authorId="4" shapeId="0" xr:uid="{E6F2F672-2090-4050-9A85-27C3181E2283}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Trading Economics consensus</t>
       </text>
     </comment>
   </commentList>
@@ -231,7 +240,7 @@
     <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-* #,##0.00\ _€_-;\-* #,##0.00\ _€_-;_-* &quot;-&quot;??\ _€_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -276,9 +285,22 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="7"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -308,7 +330,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -337,39 +359,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF008000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF000000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -380,91 +384,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>207</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>355600</xdr:colOff>
-      <xdr:row>211</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="TextBox 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18FF4AC0-C35C-CDEF-7B18-D34F28007A8A}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4759325" y="39420800"/>
-          <a:ext cx="2587625" cy="701675"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FF0000"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-GB" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="bg1"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>Reds: To Be Updated</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-FI" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -799,15 +718,18 @@
   <threadedComment ref="P1" dT="2026-06-28T06:11:48.72" personId="{AD562C04-D43F-4FA9-B7C7-504D0E54311F}" id="{C1984FB3-39AE-427D-8EF3-64A0FBB19F58}">
     <text>Average, Bloomberg</text>
   </threadedComment>
-  <threadedComment ref="D200" dT="2026-06-28T04:13:36.75" personId="{AD562C04-D43F-4FA9-B7C7-504D0E54311F}" id="{CD67C6B1-A286-4708-AD00-4F70ABEAB931}">
-    <text>Forecast Trading Economics</text>
+  <threadedComment ref="C203" dT="2026-09-30T22:54:21.94" personId="{AD562C04-D43F-4FA9-B7C7-504D0E54311F}" id="{A0063725-D041-46FA-8092-72645EA654D4}">
+    <text>Trading Economics consensus</text>
+  </threadedComment>
+  <threadedComment ref="D203" dT="2026-09-30T22:57:09.02" personId="{AD562C04-D43F-4FA9-B7C7-504D0E54311F}" id="{E6F2F672-2090-4050-9A85-27C3181E2283}">
+    <text>Trading Economics consensus</text>
   </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3101C545-B073-440C-A52B-90CA060AB682}">
-  <dimension ref="A1:G199"/>
+  <dimension ref="A1:G202"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.75">
@@ -6415,11 +6337,11 @@
       </c>
       <c r="D194" s="11">
         <f>Sheet2!H195</f>
-        <v>0.4250050348898835</v>
+        <v>0.42500503486026187</v>
       </c>
       <c r="E194" s="11">
         <f>Sheet2!I195</f>
-        <v>14.581624232904288</v>
+        <v>14.581624232764844</v>
       </c>
       <c r="F194">
         <f>Sheet2!L195</f>
@@ -6444,11 +6366,11 @@
       </c>
       <c r="D195" s="11">
         <f>Sheet2!H196</f>
-        <v>0.44716985535040815</v>
+        <v>0.44716985532447973</v>
       </c>
       <c r="E195" s="11">
         <f>Sheet2!I196</f>
-        <v>14.554431515587812</v>
+        <v>14.554431515348996</v>
       </c>
       <c r="F195">
         <f>Sheet2!L196</f>
@@ -6473,11 +6395,11 @@
       </c>
       <c r="D196" s="11">
         <f>Sheet2!H197</f>
-        <v>0.37924158366473865</v>
+        <v>0.37924138034691884</v>
       </c>
       <c r="E196" s="11">
         <f>Sheet2!I197</f>
-        <v>14.558504757834987</v>
+        <v>14.558504648664705</v>
       </c>
       <c r="F196">
         <f>Sheet2!L197</f>
@@ -6502,11 +6424,11 @@
       </c>
       <c r="D197" s="11">
         <f>Sheet2!H198</f>
-        <v>0.44967485490095382</v>
+        <v>0.4496749424406794</v>
       </c>
       <c r="E197" s="11">
         <f>Sheet2!I198</f>
-        <v>14.534569120308721</v>
+        <v>14.53456574198389</v>
       </c>
       <c r="F197">
         <f>Sheet2!L198</f>
@@ -6531,11 +6453,11 @@
       </c>
       <c r="D198" s="11">
         <f>Sheet2!H199</f>
-        <v>0.46939788848575226</v>
+        <v>0.46939781890250282</v>
       </c>
       <c r="E198" s="11">
         <f>Sheet2!I199</f>
-        <v>14.536806380218714</v>
+        <v>14.536409496568682</v>
       </c>
       <c r="F198">
         <f>Sheet2!L199</f>
@@ -6556,15 +6478,15 @@
       </c>
       <c r="C199">
         <f>Sheet2!E200</f>
-        <v>-0.14000000000000012</v>
+        <v>0.1599999999999997</v>
       </c>
       <c r="D199" s="11">
         <f>Sheet2!H200</f>
-        <v>0.46683494089523275</v>
+        <v>0.46683476220507975</v>
       </c>
       <c r="E199" s="11">
         <f>Sheet2!I200</f>
-        <v>14.546148134792231</v>
+        <v>14.4581405582506</v>
       </c>
       <c r="F199">
         <f>Sheet2!L200</f>
@@ -6573,6 +6495,93 @@
       <c r="G199" s="11">
         <f>LN(Sheet2!M200)</f>
         <v>4.498364181670282</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A200" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B200" s="5">
+        <f>LN(Sheet2!B201)</f>
+        <v>9.8013440788674249</v>
+      </c>
+      <c r="C200">
+        <f>Sheet2!E201</f>
+        <v>0.25999999999999979</v>
+      </c>
+      <c r="D200" s="11">
+        <f>Sheet2!H201</f>
+        <v>0.47543270640805013</v>
+      </c>
+      <c r="E200" s="11">
+        <f>Sheet2!I201</f>
+        <v>14.44803436908825</v>
+      </c>
+      <c r="F200">
+        <f>Sheet2!L201</f>
+        <v>2.12</v>
+      </c>
+      <c r="G200" s="11">
+        <f>LN(Sheet2!M201)</f>
+        <v>4.5364629879783003</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A201" s="4">
+        <v>46235</v>
+      </c>
+      <c r="B201" s="5">
+        <f>LN(Sheet2!B202)</f>
+        <v>9.7839154173952831</v>
+      </c>
+      <c r="C201">
+        <f>Sheet2!E202</f>
+        <v>0.52</v>
+      </c>
+      <c r="D201" s="11">
+        <f>Sheet2!H202</f>
+        <v>0.33605755450076197</v>
+      </c>
+      <c r="E201" s="11">
+        <f>Sheet2!I202</f>
+        <v>14.439324995182591</v>
+      </c>
+      <c r="F201">
+        <f>Sheet2!L202</f>
+        <v>2.12</v>
+      </c>
+      <c r="G201" s="11">
+        <f>LN(Sheet2!M202)</f>
+        <v>4.4375795937941307</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.75">
+      <c r="A202" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B202" s="5">
+        <f>LN(Sheet2!B203)</f>
+        <v>9.7912702494150885</v>
+      </c>
+      <c r="C202">
+        <f>Sheet2!E203</f>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="D202" s="11">
+        <f>Sheet2!H203</f>
+        <v>0.52637803223245072</v>
+      </c>
+      <c r="E202" s="11">
+        <f>Sheet2!I203</f>
+        <v>14.447930308444844</v>
+      </c>
+      <c r="F202">
+        <f>Sheet2!L203</f>
+        <v>1.87</v>
+      </c>
+      <c r="G202" s="11">
+        <f>LN(Sheet2!M203)</f>
+        <v>4.512945241945574</v>
       </c>
     </row>
   </sheetData>
@@ -6582,7 +6591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25619763-56A8-487F-AB71-E6EA9E15A0D1}">
-  <dimension ref="A1:P200"/>
+  <dimension ref="A1:P203"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="2" max="2" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
@@ -6593,17 +6602,18 @@
     <col min="8" max="8" width="9.54296875" style="1" customWidth="1"/>
     <col min="9" max="9" width="8.7265625" style="1"/>
     <col min="12" max="13" width="8.7265625" style="1"/>
-    <col min="15" max="15" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.76953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="9.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.75">
       <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="22"/>
+      <c r="D1" s="23"/>
       <c r="E1" s="3" t="s">
         <v>8</v>
       </c>
@@ -6702,10 +6712,10 @@
       <c r="M3" s="6">
         <v>191.34247619047619</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="21">
         <v>9365</v>
       </c>
-      <c r="P3" s="20">
+      <c r="P3" s="21">
         <v>9285.6666666666661</v>
       </c>
     </row>
@@ -6756,10 +6766,10 @@
       <c r="M4" s="6">
         <v>202.83085000000003</v>
       </c>
-      <c r="O4" s="20">
+      <c r="O4" s="21">
         <v>9335</v>
       </c>
-      <c r="P4" s="20">
+      <c r="P4" s="21">
         <v>9344.9</v>
       </c>
     </row>
@@ -6810,10 +6820,10 @@
       <c r="M5" s="6">
         <v>163.08356521739125</v>
       </c>
-      <c r="O5" s="20">
+      <c r="O5" s="21">
         <v>9115</v>
       </c>
-      <c r="P5" s="20">
+      <c r="P5" s="21">
         <v>9167</v>
       </c>
     </row>
@@ -6864,10 +6874,10 @@
       <c r="M6" s="6">
         <v>159.84154545454547</v>
       </c>
-      <c r="O6" s="20">
+      <c r="O6" s="21">
         <v>9012</v>
       </c>
-      <c r="P6" s="20">
+      <c r="P6" s="21">
         <v>9030.4090909090901</v>
       </c>
     </row>
@@ -6918,10 +6928,10 @@
       <c r="M7" s="6">
         <v>186.46042857142854</v>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="21">
         <v>9180</v>
       </c>
-      <c r="P7" s="20">
+      <c r="P7" s="21">
         <v>9172.9047619047615</v>
       </c>
     </row>
@@ -6972,10 +6982,10 @@
       <c r="M8" s="6">
         <v>182.34554545454546</v>
       </c>
-      <c r="O8" s="20">
+      <c r="O8" s="21">
         <v>9083</v>
       </c>
-      <c r="P8" s="20">
+      <c r="P8" s="21">
         <v>9146.2727272727279</v>
       </c>
     </row>
@@ -7026,10 +7036,10 @@
       <c r="M9" s="6">
         <v>166.68695454545457</v>
       </c>
-      <c r="O9" s="20">
+      <c r="O9" s="21">
         <v>8952</v>
       </c>
-      <c r="P9" s="20">
+      <c r="P9" s="21">
         <v>9041.318181818182</v>
       </c>
     </row>
@@ -7080,10 +7090,10 @@
       <c r="M10" s="6">
         <v>152.44131818181816</v>
       </c>
-      <c r="O10" s="20">
+      <c r="O10" s="21">
         <v>9041</v>
       </c>
-      <c r="P10" s="20">
+      <c r="P10" s="21">
         <v>8972.4090909090901</v>
       </c>
     </row>
@@ -7134,10 +7144,10 @@
       <c r="M11" s="6">
         <v>149.64409090909092</v>
       </c>
-      <c r="O11" s="20">
+      <c r="O11" s="21">
         <v>8924</v>
       </c>
-      <c r="P11" s="20">
+      <c r="P11" s="21">
         <v>8974.181818181818</v>
       </c>
     </row>
@@ -7188,10 +7198,10 @@
       <c r="M12" s="6">
         <v>131.21904761904761</v>
       </c>
-      <c r="O12" s="20">
+      <c r="O12" s="21">
         <v>8928</v>
       </c>
-      <c r="P12" s="20">
+      <c r="P12" s="21">
         <v>8930.0476190476184</v>
       </c>
     </row>
@@ -7242,10 +7252,10 @@
       <c r="M13" s="6">
         <v>137.55540909090908</v>
       </c>
-      <c r="O13" s="20">
+      <c r="O13" s="21">
         <v>9013</v>
       </c>
-      <c r="P13" s="20">
+      <c r="P13" s="21">
         <v>8943.363636363636</v>
       </c>
     </row>
@@ -7296,10 +7306,10 @@
       <c r="M14" s="6">
         <v>131.19230434782611</v>
       </c>
-      <c r="O14" s="20">
+      <c r="O14" s="21">
         <v>8991</v>
       </c>
-      <c r="P14" s="20">
+      <c r="P14" s="21">
         <v>9025</v>
       </c>
     </row>
@@ -7350,10 +7360,10 @@
       <c r="M15" s="6">
         <v>141.62828571428571</v>
       </c>
-      <c r="O15" s="20">
+      <c r="O15" s="21">
         <v>9057</v>
       </c>
-      <c r="P15" s="20">
+      <c r="P15" s="21">
         <v>9037.4761904761908</v>
       </c>
     </row>
@@ -7404,10 +7414,10 @@
       <c r="M16" s="6">
         <v>151.89179999999999</v>
       </c>
-      <c r="O16" s="20">
+      <c r="O16" s="21">
         <v>8823</v>
       </c>
-      <c r="P16" s="20">
+      <c r="P16" s="21">
         <v>8918.7999999999993</v>
       </c>
     </row>
@@ -7458,10 +7468,10 @@
       <c r="M17" s="6">
         <v>145.0194347826087</v>
       </c>
-      <c r="O17" s="20">
+      <c r="O17" s="21">
         <v>8709</v>
       </c>
-      <c r="P17" s="20">
+      <c r="P17" s="21">
         <v>8762.217391304348</v>
       </c>
     </row>
@@ -7512,10 +7522,10 @@
       <c r="M18" s="6">
         <v>139.65299999999999</v>
       </c>
-      <c r="O18" s="20">
+      <c r="O18" s="21">
         <v>8574</v>
       </c>
-      <c r="P18" s="20">
+      <c r="P18" s="21">
         <v>8650.5238095238092</v>
       </c>
     </row>
@@ -7566,10 +7576,10 @@
       <c r="M19" s="6">
         <v>134.52895454545455</v>
       </c>
-      <c r="O19" s="20">
+      <c r="O19" s="21">
         <v>8537</v>
       </c>
-      <c r="P19" s="20">
+      <c r="P19" s="21">
         <v>8560.318181818182</v>
       </c>
     </row>
@@ -7620,10 +7630,10 @@
       <c r="M20" s="6">
         <v>138.42363636363635</v>
       </c>
-      <c r="O20" s="20">
+      <c r="O20" s="21">
         <v>8597</v>
       </c>
-      <c r="P20" s="20">
+      <c r="P20" s="21">
         <v>8565.4090909090901</v>
       </c>
     </row>
@@ -7674,10 +7684,10 @@
       <c r="M21" s="6">
         <v>137.48757142857144</v>
       </c>
-      <c r="O21" s="20">
+      <c r="O21" s="21">
         <v>8508</v>
       </c>
-      <c r="P21" s="20">
+      <c r="P21" s="21">
         <v>8530.7619047619046</v>
       </c>
     </row>
@@ -7728,10 +7738,10 @@
       <c r="M22" s="6">
         <v>159.51395652173909</v>
       </c>
-      <c r="O22" s="20">
+      <c r="O22" s="21">
         <v>8578</v>
       </c>
-      <c r="P22" s="20">
+      <c r="P22" s="21">
         <v>8529.173913043478</v>
       </c>
     </row>
@@ -7782,10 +7792,10 @@
       <c r="M23" s="6">
         <v>212.14381818181812</v>
       </c>
-      <c r="O23" s="20">
+      <c r="O23" s="21">
         <v>8823</v>
       </c>
-      <c r="P23" s="20">
+      <c r="P23" s="21">
         <v>8729.454545454546</v>
       </c>
     </row>
@@ -7836,10 +7846,10 @@
       <c r="M24" s="6">
         <v>245.83776190476189</v>
       </c>
-      <c r="O24" s="20">
+      <c r="O24" s="21">
         <v>8835</v>
       </c>
-      <c r="P24" s="20">
+      <c r="P24" s="21">
         <v>8865.3333333333339</v>
       </c>
     </row>
@@ -7890,10 +7900,10 @@
       <c r="M25" s="6">
         <v>218.20772727272725</v>
       </c>
-      <c r="O25" s="20">
+      <c r="O25" s="21">
         <v>9170</v>
       </c>
-      <c r="P25" s="20">
+      <c r="P25" s="21">
         <v>9005</v>
       </c>
     </row>
@@ -7944,10 +7954,10 @@
       <c r="M26" s="6">
         <v>208.92922727272725</v>
       </c>
-      <c r="O26" s="20">
+      <c r="O26" s="21">
         <v>9068</v>
       </c>
-      <c r="P26" s="20">
+      <c r="P26" s="21">
         <v>9067.0909090909099</v>
       </c>
     </row>
@@ -7998,10 +8008,10 @@
       <c r="M27" s="6">
         <v>203.43472727272726</v>
       </c>
-      <c r="O27" s="20">
+      <c r="O27" s="21">
         <v>9000</v>
       </c>
-      <c r="P27" s="20">
+      <c r="P27" s="21">
         <v>9066.863636363636</v>
       </c>
     </row>
@@ -8052,10 +8062,10 @@
       <c r="M28" s="6">
         <v>162.49876190476192</v>
       </c>
-      <c r="O28" s="20">
+      <c r="O28" s="21">
         <v>9085</v>
       </c>
-      <c r="P28" s="20">
+      <c r="P28" s="21">
         <v>9035.6666666666661</v>
       </c>
     </row>
@@ -8106,10 +8116,10 @@
       <c r="M29" s="6">
         <v>160.37854545454545</v>
       </c>
-      <c r="O29" s="20">
+      <c r="O29" s="21">
         <v>9180</v>
       </c>
-      <c r="P29" s="20">
+      <c r="P29" s="21">
         <v>9158.045454545454</v>
       </c>
     </row>
@@ -8160,10 +8170,10 @@
       <c r="M30" s="6">
         <v>170.10085714285717</v>
       </c>
-      <c r="O30" s="20">
+      <c r="O30" s="21">
         <v>9190</v>
       </c>
-      <c r="P30" s="20">
+      <c r="P30" s="21">
         <v>9175</v>
       </c>
     </row>
@@ -8214,10 +8224,10 @@
       <c r="M31" s="6">
         <v>202.28491304347821</v>
       </c>
-      <c r="O31" s="20">
+      <c r="O31" s="21">
         <v>9565</v>
       </c>
-      <c r="P31" s="20">
+      <c r="P31" s="21">
         <v>9316.5217391304341</v>
       </c>
     </row>
@@ -8268,10 +8278,10 @@
       <c r="M32" s="6">
         <v>211.08776190476189</v>
       </c>
-      <c r="O32" s="20">
+      <c r="O32" s="21">
         <v>9480</v>
       </c>
-      <c r="P32" s="20">
+      <c r="P32" s="21">
         <v>9431.6190476190477</v>
       </c>
     </row>
@@ -8322,10 +8332,10 @@
       <c r="M33" s="6">
         <v>183.33040909090911</v>
       </c>
-      <c r="O33" s="20">
+      <c r="O33" s="21">
         <v>9485</v>
       </c>
-      <c r="P33" s="20">
+      <c r="P33" s="21">
         <v>9441.181818181818</v>
       </c>
     </row>
@@ -8376,10 +8386,10 @@
       <c r="M34" s="6">
         <v>174.69426086956523</v>
       </c>
-      <c r="O34" s="20">
+      <c r="O34" s="21">
         <v>9560</v>
       </c>
-      <c r="P34" s="20">
+      <c r="P34" s="21">
         <v>9505.434782608696</v>
       </c>
     </row>
@@ -8430,10 +8440,10 @@
       <c r="M35" s="6">
         <v>168.10974999999999</v>
       </c>
-      <c r="O35" s="20">
+      <c r="O35" s="21">
         <v>9588</v>
       </c>
-      <c r="P35" s="20">
+      <c r="P35" s="21">
         <v>9564.7999999999993</v>
       </c>
     </row>
@@ -8484,10 +8494,10 @@
       <c r="M36" s="6">
         <v>165.55799999999999</v>
       </c>
-      <c r="O36" s="20">
+      <c r="O36" s="21">
         <v>9615</v>
       </c>
-      <c r="P36" s="20">
+      <c r="P36" s="21">
         <v>9599.2608695652179</v>
       </c>
     </row>
@@ -8538,10 +8548,10 @@
       <c r="M37" s="6">
         <v>165.55799999999999</v>
       </c>
-      <c r="O37" s="20">
+      <c r="O37" s="21">
         <v>9605</v>
       </c>
-      <c r="P37" s="20">
+      <c r="P37" s="21">
         <v>9620.136363636364</v>
       </c>
     </row>
@@ -8592,10 +8602,10 @@
       <c r="M38" s="6">
         <v>133.89519047619044</v>
       </c>
-      <c r="O38" s="20">
+      <c r="O38" s="21">
         <v>9670</v>
       </c>
-      <c r="P38" s="20">
+      <c r="P38" s="21">
         <v>9646.0476190476184</v>
       </c>
     </row>
@@ -8646,10 +8656,10 @@
       <c r="M39" s="6">
         <v>134.6097391304348</v>
       </c>
-      <c r="O39" s="20">
+      <c r="O39" s="21">
         <v>9698</v>
       </c>
-      <c r="P39" s="20">
+      <c r="P39" s="21">
         <v>9654.3043478260861</v>
       </c>
     </row>
@@ -8700,10 +8710,10 @@
       <c r="M40" s="6">
         <v>142.51524999999998</v>
       </c>
-      <c r="O40" s="20">
+      <c r="O40" s="21">
         <v>9667</v>
       </c>
-      <c r="P40" s="20">
+      <c r="P40" s="21">
         <v>9680.75</v>
       </c>
     </row>
@@ -8754,10 +8764,10 @@
       <c r="M41" s="6">
         <v>139.25942857142857</v>
       </c>
-      <c r="O41" s="20">
+      <c r="O41" s="21">
         <v>9719</v>
       </c>
-      <c r="P41" s="20">
+      <c r="P41" s="21">
         <v>9708.4285714285706</v>
       </c>
     </row>
@@ -8808,10 +8818,10 @@
       <c r="M42" s="6">
         <v>146.49922727272727</v>
       </c>
-      <c r="O42" s="20">
+      <c r="O42" s="21">
         <v>9722</v>
       </c>
-      <c r="P42" s="20">
+      <c r="P42" s="21">
         <v>9723.636363636364</v>
       </c>
     </row>
@@ -8862,10 +8872,10 @@
       <c r="M43" s="6">
         <v>137.90939130434782</v>
       </c>
-      <c r="O43" s="20">
+      <c r="O43" s="21">
         <v>9802</v>
       </c>
-      <c r="P43" s="20">
+      <c r="P43" s="21">
         <v>9759.652173913044</v>
       </c>
     </row>
@@ -8916,10 +8926,10 @@
       <c r="M44" s="6">
         <v>211.74079999999995</v>
       </c>
-      <c r="O44" s="20">
+      <c r="O44" s="21">
         <v>9929</v>
       </c>
-      <c r="P44" s="20">
+      <c r="P44" s="21">
         <v>9871.7000000000007</v>
       </c>
     </row>
@@ -8970,10 +8980,10 @@
       <c r="M45" s="6">
         <v>208.34808695652183</v>
       </c>
-      <c r="O45" s="20">
+      <c r="O45" s="21">
         <v>10278</v>
       </c>
-      <c r="P45" s="20">
+      <c r="P45" s="21">
         <v>10071.478260869566</v>
       </c>
     </row>
@@ -9024,10 +9034,10 @@
       <c r="M46" s="6">
         <v>244.53031818181816</v>
       </c>
-      <c r="O46" s="20">
+      <c r="O46" s="21">
         <v>10924</v>
       </c>
-      <c r="P46" s="20">
+      <c r="P46" s="21">
         <v>10532.545454545454</v>
       </c>
     </row>
@@ -9078,10 +9088,10 @@
       <c r="M47" s="6">
         <v>281.72300000000001</v>
       </c>
-      <c r="O47" s="20">
+      <c r="O47" s="21">
         <v>11613</v>
       </c>
-      <c r="P47" s="20">
+      <c r="P47" s="21">
         <v>11327.476190476191</v>
       </c>
     </row>
@@ -9132,10 +9142,10 @@
       <c r="M48" s="6">
         <v>262.24773913043481</v>
       </c>
-      <c r="O48" s="20">
+      <c r="O48" s="21">
         <v>11234</v>
       </c>
-      <c r="P48" s="20">
+      <c r="P48" s="21">
         <v>11345.130434782608</v>
       </c>
     </row>
@@ -9186,10 +9196,10 @@
       <c r="M49" s="6">
         <v>223.61804761904764</v>
       </c>
-      <c r="O49" s="20">
+      <c r="O49" s="21">
         <v>11977</v>
       </c>
-      <c r="P49" s="20">
+      <c r="P49" s="21">
         <v>11610.666666666666</v>
       </c>
     </row>
@@ -9240,10 +9250,10 @@
       <c r="M50" s="6">
         <v>224.41749999999999</v>
       </c>
-      <c r="O50" s="20">
+      <c r="O50" s="21">
         <v>12189</v>
       </c>
-      <c r="P50" s="20">
+      <c r="P50" s="21">
         <v>12086.727272727272</v>
       </c>
     </row>
@@ -9294,10 +9304,10 @@
       <c r="M51" s="6">
         <v>228.61734782608693</v>
       </c>
-      <c r="O51" s="20">
+      <c r="O51" s="21">
         <v>12226</v>
       </c>
-      <c r="P51" s="20">
+      <c r="P51" s="21">
         <v>12158.347826086956</v>
       </c>
     </row>
@@ -9348,10 +9358,10 @@
       <c r="M52" s="6">
         <v>209.85519999999997</v>
       </c>
-      <c r="O52" s="20">
+      <c r="O52" s="21">
         <v>11634</v>
       </c>
-      <c r="P52" s="20">
+      <c r="P52" s="21">
         <v>11919.8</v>
       </c>
     </row>
@@ -9402,10 +9412,10 @@
       <c r="M53" s="6">
         <v>181.97395238095237</v>
       </c>
-      <c r="O53" s="20">
+      <c r="O53" s="21">
         <v>11404</v>
       </c>
-      <c r="P53" s="20">
+      <c r="P53" s="21">
         <v>11416.857142857143</v>
       </c>
     </row>
@@ -9456,10 +9466,10 @@
       <c r="M54" s="6">
         <v>171.83245454545451</v>
       </c>
-      <c r="O54" s="20">
+      <c r="O54" s="21">
         <v>11532</v>
       </c>
-      <c r="P54" s="20">
+      <c r="P54" s="21">
         <v>11431.545454545454</v>
       </c>
     </row>
@@ -9510,10 +9520,10 @@
       <c r="M55" s="6">
         <v>155.29827272727269</v>
       </c>
-      <c r="O55" s="20">
+      <c r="O55" s="21">
         <v>11611</v>
       </c>
-      <c r="P55" s="20">
+      <c r="P55" s="21">
         <v>11536.272727272728</v>
       </c>
     </row>
@@ -9564,10 +9574,10 @@
       <c r="M56" s="6">
         <v>147.9182857142857</v>
       </c>
-      <c r="O56" s="20">
+      <c r="O56" s="21">
         <v>11969</v>
       </c>
-      <c r="P56" s="20">
+      <c r="P56" s="21">
         <v>11892.523809523809</v>
       </c>
     </row>
@@ -9618,10 +9628,10 @@
       <c r="M57" s="6">
         <v>148.47921739130433</v>
       </c>
-      <c r="O57" s="20">
+      <c r="O57" s="21">
         <v>11591</v>
       </c>
-      <c r="P57" s="20">
+      <c r="P57" s="21">
         <v>11663.608695652174</v>
       </c>
     </row>
@@ -9672,10 +9682,10 @@
       <c r="M58" s="6">
         <v>147.81885714285713</v>
       </c>
-      <c r="O58" s="20">
+      <c r="O58" s="21">
         <v>11717</v>
       </c>
-      <c r="P58" s="20">
+      <c r="P58" s="21">
         <v>11710.904761904761</v>
       </c>
     </row>
@@ -9726,10 +9736,10 @@
       <c r="M59" s="6">
         <v>140.39736363636365</v>
       </c>
-      <c r="O59" s="20">
+      <c r="O59" s="21">
         <v>12212</v>
       </c>
-      <c r="P59" s="20">
+      <c r="P59" s="21">
         <v>11898.59090909091</v>
       </c>
     </row>
@@ -9780,10 +9790,10 @@
       <c r="M60" s="6">
         <v>162.09878260869564</v>
       </c>
-      <c r="O60" s="20">
+      <c r="O60" s="21">
         <v>12082</v>
       </c>
-      <c r="P60" s="20">
+      <c r="P60" s="21">
         <v>12142.04347826087</v>
       </c>
     </row>
@@ -9834,10 +9844,10 @@
       <c r="M61" s="6">
         <v>141.33325000000002</v>
       </c>
-      <c r="O61" s="20">
+      <c r="O61" s="21">
         <v>12196</v>
       </c>
-      <c r="P61" s="20">
+      <c r="P61" s="21">
         <v>12166.9</v>
       </c>
     </row>
@@ -9888,10 +9898,10 @@
       <c r="M62" s="6">
         <v>160.62560869565223</v>
       </c>
-      <c r="O62" s="20">
+      <c r="O62" s="21">
         <v>12440</v>
       </c>
-      <c r="P62" s="20">
+      <c r="P62" s="21">
         <v>12431.565217391304</v>
       </c>
     </row>
@@ -9942,10 +9952,10 @@
       <c r="M63" s="6">
         <v>163.68454545454549</v>
       </c>
-      <c r="O63" s="20">
+      <c r="O63" s="21">
         <v>12625</v>
       </c>
-      <c r="P63" s="20">
+      <c r="P63" s="21">
         <v>12573.59090909091</v>
       </c>
     </row>
@@ -9996,10 +10006,10 @@
       <c r="M64" s="6">
         <v>150.06445000000002</v>
       </c>
-      <c r="O64" s="20">
+      <c r="O64" s="21">
         <v>12863</v>
       </c>
-      <c r="P64" s="20">
+      <c r="P64" s="21">
         <v>12762.75</v>
       </c>
     </row>
@@ -10050,10 +10060,10 @@
       <c r="M65" s="6">
         <v>152.01759090909093</v>
       </c>
-      <c r="O65" s="20">
+      <c r="O65" s="21">
         <v>13084</v>
       </c>
-      <c r="P65" s="20">
+      <c r="P65" s="21">
         <v>13067.363636363636</v>
       </c>
     </row>
@@ -10104,10 +10114,10 @@
       <c r="M66" s="6">
         <v>157.65195454545452</v>
       </c>
-      <c r="O66" s="20">
+      <c r="O66" s="21">
         <v>12937</v>
       </c>
-      <c r="P66" s="20">
+      <c r="P66" s="21">
         <v>12947.59090909091</v>
       </c>
     </row>
@@ -10158,10 +10168,10 @@
       <c r="M67" s="6">
         <v>164.48228571428569</v>
       </c>
-      <c r="O67" s="20">
+      <c r="O67" s="21">
         <v>13211</v>
       </c>
-      <c r="P67" s="20">
+      <c r="P67" s="21">
         <v>13133.238095238095</v>
       </c>
     </row>
@@ -10212,10 +10222,10 @@
       <c r="M68" s="6">
         <v>172.51095454545452</v>
       </c>
-      <c r="O68" s="20">
+      <c r="O68" s="21">
         <v>13332</v>
       </c>
-      <c r="P68" s="20">
+      <c r="P68" s="21">
         <v>13305.90909090909</v>
       </c>
     </row>
@@ -10266,10 +10276,10 @@
       <c r="M69" s="6">
         <v>172.86465217391304</v>
       </c>
-      <c r="O69" s="20">
+      <c r="O69" s="21">
         <v>13481</v>
       </c>
-      <c r="P69" s="20">
+      <c r="P69" s="21">
         <v>13376.565217391304</v>
       </c>
     </row>
@@ -10320,10 +10330,10 @@
       <c r="M70" s="6">
         <v>211.23342857142862</v>
       </c>
-      <c r="O70" s="20">
+      <c r="O70" s="21">
         <v>14027</v>
       </c>
-      <c r="P70" s="20">
+      <c r="P70" s="21">
         <v>13789.952380952382</v>
       </c>
     </row>
@@ -10374,10 +10384,10 @@
       <c r="M71" s="6">
         <v>246.19090909090912</v>
       </c>
-      <c r="O71" s="20">
+      <c r="O71" s="21">
         <v>14657</v>
       </c>
-      <c r="P71" s="20">
+      <c r="P71" s="21">
         <v>14411.045454545454</v>
       </c>
     </row>
@@ -10428,10 +10438,10 @@
       <c r="M72" s="6">
         <v>228.3147727272727</v>
       </c>
-      <c r="O72" s="20">
+      <c r="O72" s="21">
         <v>13639</v>
       </c>
-      <c r="P72" s="20">
+      <c r="P72" s="21">
         <v>13777.59090909091</v>
       </c>
     </row>
@@ -10482,10 +10492,10 @@
       <c r="M73" s="6">
         <v>217.1787619047619</v>
       </c>
-      <c r="O73" s="20">
+      <c r="O73" s="21">
         <v>13840</v>
       </c>
-      <c r="P73" s="20">
+      <c r="P73" s="21">
         <v>13677.333333333334</v>
       </c>
     </row>
@@ -10536,10 +10546,10 @@
       <c r="M74" s="6">
         <v>236.62921739130437</v>
       </c>
-      <c r="O74" s="20">
+      <c r="O74" s="21">
         <v>13795</v>
       </c>
-      <c r="P74" s="20">
+      <c r="P74" s="21">
         <v>13836.173913043478</v>
       </c>
     </row>
@@ -10590,10 +10600,10 @@
       <c r="M75" s="6">
         <v>244.64495238095242</v>
       </c>
-      <c r="O75" s="20">
+      <c r="O75" s="21">
         <v>13846</v>
       </c>
-      <c r="P75" s="20">
+      <c r="P75" s="21">
         <v>13887.190476190477</v>
       </c>
     </row>
@@ -10644,10 +10654,10 @@
       <c r="M76" s="6">
         <v>243.35871428571434</v>
       </c>
-      <c r="O76" s="20">
+      <c r="O76" s="21">
         <v>13395</v>
       </c>
-      <c r="P76" s="20">
+      <c r="P76" s="21">
         <v>13513.380952380952</v>
       </c>
     </row>
@@ -10698,10 +10708,10 @@
       <c r="M77" s="6">
         <v>204.34500000000003</v>
       </c>
-      <c r="O77" s="20">
+      <c r="O77" s="21">
         <v>13276</v>
       </c>
-      <c r="P77" s="20">
+      <c r="P77" s="21">
         <v>13198.826086956522</v>
       </c>
     </row>
@@ -10752,10 +10762,10 @@
       <c r="M78" s="6">
         <v>198.41947619047616</v>
       </c>
-      <c r="O78" s="20">
+      <c r="O78" s="21">
         <v>13204</v>
       </c>
-      <c r="P78" s="20">
+      <c r="P78" s="21">
         <v>13172.857142857143</v>
       </c>
     </row>
@@ -10806,10 +10816,10 @@
       <c r="M79" s="6">
         <v>190.16877272727277</v>
       </c>
-      <c r="O79" s="20">
+      <c r="O79" s="21">
         <v>13615</v>
       </c>
-      <c r="P79" s="20">
+      <c r="P79" s="21">
         <v>13416.90909090909</v>
       </c>
     </row>
@@ -10860,10 +10870,10 @@
       <c r="M80" s="6">
         <v>192.41354545454544</v>
       </c>
-      <c r="O80" s="20">
+      <c r="O80" s="21">
         <v>13180</v>
       </c>
-      <c r="P80" s="20">
+      <c r="P80" s="21">
         <v>13338.045454545454</v>
       </c>
     </row>
@@ -10914,10 +10924,10 @@
       <c r="M81" s="6">
         <v>168.7737619047619</v>
       </c>
-      <c r="O81" s="20">
+      <c r="O81" s="21">
         <v>13094</v>
       </c>
-      <c r="P81" s="20">
+      <c r="P81" s="21">
         <v>13117.619047619048</v>
       </c>
     </row>
@@ -10968,10 +10978,10 @@
       <c r="M82" s="6">
         <v>146.45617391304344</v>
       </c>
-      <c r="O82" s="20">
+      <c r="O82" s="21">
         <v>13300</v>
       </c>
-      <c r="P82" s="20">
+      <c r="P82" s="21">
         <v>13160.608695652174</v>
       </c>
     </row>
@@ -11022,10 +11032,10 @@
       <c r="M83" s="6">
         <v>145.49236363636365</v>
       </c>
-      <c r="O83" s="20">
+      <c r="O83" s="21">
         <v>12998</v>
       </c>
-      <c r="P83" s="20">
+      <c r="P83" s="21">
         <v>13110</v>
       </c>
     </row>
@@ -11076,10 +11086,10 @@
       <c r="M84" s="6">
         <v>151.74176190476194</v>
       </c>
-      <c r="O84" s="20">
+      <c r="O84" s="21">
         <v>13051</v>
       </c>
-      <c r="P84" s="20">
+      <c r="P84" s="21">
         <v>13018.380952380952</v>
       </c>
     </row>
@@ -11130,10 +11140,10 @@
       <c r="M85" s="6">
         <v>170.87813636363637</v>
       </c>
-      <c r="O85" s="20">
+      <c r="O85" s="21">
         <v>13563</v>
       </c>
-      <c r="P85" s="20">
+      <c r="P85" s="21">
         <v>13314.954545454546</v>
       </c>
     </row>
@@ -11184,10 +11194,10 @@
       <c r="M86" s="6">
         <v>163.19881818181821</v>
       </c>
-      <c r="O86" s="20">
+      <c r="O86" s="21">
         <v>13436</v>
       </c>
-      <c r="P86" s="20">
+      <c r="P86" s="21">
         <v>13409.818181818182</v>
       </c>
     </row>
@@ -11238,10 +11248,10 @@
       <c r="M87" s="6">
         <v>151.86809090909094</v>
       </c>
-      <c r="O87" s="20">
+      <c r="O87" s="21">
         <v>13343</v>
       </c>
-      <c r="P87" s="20">
+      <c r="P87" s="21">
         <v>13366.09090909091</v>
       </c>
     </row>
@@ -11292,10 +11302,10 @@
       <c r="M88" s="6">
         <v>136.8956</v>
       </c>
-      <c r="O88" s="20">
+      <c r="O88" s="21">
         <v>13347</v>
       </c>
-      <c r="P88" s="20">
+      <c r="P88" s="21">
         <v>13337.75</v>
       </c>
     </row>
@@ -11346,10 +11356,10 @@
       <c r="M89" s="6">
         <v>128.88608695652175</v>
       </c>
-      <c r="O89" s="20">
+      <c r="O89" s="21">
         <v>13321</v>
       </c>
-      <c r="P89" s="20">
+      <c r="P89" s="21">
         <v>13343.260869565218</v>
       </c>
     </row>
@@ -11400,10 +11410,10 @@
       <c r="M90" s="6">
         <v>131.84299999999999</v>
       </c>
-      <c r="O90" s="20">
+      <c r="O90" s="21">
         <v>13327</v>
       </c>
-      <c r="P90" s="20">
+      <c r="P90" s="21">
         <v>13302.2</v>
       </c>
     </row>
@@ -11454,10 +11464,10 @@
       <c r="M91" s="6">
         <v>125.85113043478263</v>
       </c>
-      <c r="O91" s="20">
+      <c r="O91" s="21">
         <v>13321</v>
       </c>
-      <c r="P91" s="20">
+      <c r="P91" s="21">
         <v>13322.565217391304</v>
       </c>
     </row>
@@ -11508,10 +11518,10 @@
       <c r="M92" s="6">
         <v>116.95295454545455</v>
       </c>
-      <c r="O92" s="20">
+      <c r="O92" s="21">
         <v>13319</v>
       </c>
-      <c r="P92" s="20">
+      <c r="P92" s="21">
         <v>13307.045454545454</v>
       </c>
     </row>
@@ -11562,10 +11572,10 @@
       <c r="M93" s="6">
         <v>115.39385714285713</v>
       </c>
-      <c r="O93" s="20">
+      <c r="O93" s="21">
         <v>13323</v>
       </c>
-      <c r="P93" s="20">
+      <c r="P93" s="21">
         <v>13346.571428571429</v>
       </c>
     </row>
@@ -11616,10 +11626,10 @@
       <c r="M94" s="6">
         <v>108.89913043478262</v>
       </c>
-      <c r="O94" s="20">
+      <c r="O94" s="21">
         <v>13351</v>
       </c>
-      <c r="P94" s="20">
+      <c r="P94" s="21">
         <v>13343.130434782608</v>
       </c>
     </row>
@@ -11670,10 +11680,10 @@
       <c r="M95" s="6">
         <v>99.948761904761909</v>
       </c>
-      <c r="O95" s="20">
+      <c r="O95" s="21">
         <v>13492</v>
       </c>
-      <c r="P95" s="20">
+      <c r="P95" s="21">
         <v>13307.571428571429</v>
       </c>
     </row>
@@ -11724,10 +11734,10 @@
       <c r="M96" s="6">
         <v>97.784772727272724</v>
       </c>
-      <c r="O96" s="20">
+      <c r="O96" s="21">
         <v>13572</v>
       </c>
-      <c r="P96" s="20">
+      <c r="P96" s="21">
         <v>13528.318181818182</v>
       </c>
     </row>
@@ -11778,10 +11788,10 @@
       <c r="M97" s="6">
         <v>97.763454545454536</v>
       </c>
-      <c r="O97" s="20">
+      <c r="O97" s="21">
         <v>13514</v>
       </c>
-      <c r="P97" s="20">
+      <c r="P97" s="21">
         <v>13527.272727272728</v>
       </c>
     </row>
@@ -11832,10 +11842,10 @@
       <c r="M98" s="6">
         <v>90.532095238095252</v>
       </c>
-      <c r="O98" s="20">
+      <c r="O98" s="21">
         <v>13548</v>
       </c>
-      <c r="P98" s="20">
+      <c r="P98" s="21">
         <v>13559.333333333334</v>
       </c>
     </row>
@@ -11886,10 +11896,10 @@
       <c r="M99" s="6">
         <v>80.348043478260848</v>
       </c>
-      <c r="O99" s="20">
+      <c r="O99" s="21">
         <v>13413</v>
       </c>
-      <c r="P99" s="20">
+      <c r="P99" s="21">
         <v>13388.08695652174</v>
       </c>
     </row>
@@ -11940,10 +11950,10 @@
       <c r="M100" s="6">
         <v>87.574499999999986</v>
       </c>
-      <c r="O100" s="20">
+      <c r="O100" s="21">
         <v>13707</v>
       </c>
-      <c r="P100" s="20">
+      <c r="P100" s="21">
         <v>13601.7</v>
       </c>
     </row>
@@ -11994,10 +12004,10 @@
       <c r="M101" s="6">
         <v>94.428045454545469</v>
       </c>
-      <c r="O101" s="20">
+      <c r="O101" s="21">
         <v>13756</v>
       </c>
-      <c r="P101" s="20">
+      <c r="P101" s="21">
         <v>13760.727272727272</v>
       </c>
     </row>
@@ -12048,10 +12058,10 @@
       <c r="M102" s="6">
         <v>100.70242857142858</v>
       </c>
-      <c r="O102" s="20">
+      <c r="O102" s="21">
         <v>13877</v>
       </c>
-      <c r="P102" s="20">
+      <c r="P102" s="21">
         <v>13809.095238095239</v>
       </c>
     </row>
@@ -12102,10 +12112,10 @@
       <c r="M103" s="6">
         <v>118.39917391304348</v>
       </c>
-      <c r="O103" s="20">
+      <c r="O103" s="21">
         <v>13951</v>
       </c>
-      <c r="P103" s="20">
+      <c r="P103" s="21">
         <v>14038.347826086956</v>
       </c>
     </row>
@@ -12156,10 +12166,10 @@
       <c r="M104" s="6">
         <v>130.93471428571428</v>
       </c>
-      <c r="O104" s="20">
+      <c r="O104" s="21">
         <v>14404</v>
       </c>
-      <c r="P104" s="20">
+      <c r="P104" s="21">
         <v>14007.190476190477</v>
       </c>
     </row>
@@ -12210,10 +12220,10 @@
       <c r="M105" s="6">
         <v>121.41877272727274</v>
       </c>
-      <c r="O105" s="20">
+      <c r="O105" s="21">
         <v>14413</v>
       </c>
-      <c r="P105" s="20">
+      <c r="P105" s="21">
         <v>14410</v>
       </c>
     </row>
@@ -12264,10 +12274,10 @@
       <c r="M106" s="6">
         <v>118.65352173913043</v>
       </c>
-      <c r="O106" s="20">
+      <c r="O106" s="21">
         <v>14711</v>
       </c>
-      <c r="P106" s="20">
+      <c r="P106" s="21">
         <v>14564.91304347826</v>
       </c>
     </row>
@@ -12318,10 +12328,10 @@
       <c r="M107" s="6">
         <v>137.0829</v>
       </c>
-      <c r="O107" s="20">
+      <c r="O107" s="21">
         <v>14929</v>
       </c>
-      <c r="P107" s="20">
+      <c r="P107" s="21">
         <v>14869.7</v>
       </c>
     </row>
@@ -12372,10 +12382,10 @@
       <c r="M108" s="6">
         <v>147.58617391304352</v>
       </c>
-      <c r="O108" s="20">
+      <c r="O108" s="21">
         <v>15227</v>
       </c>
-      <c r="P108" s="20">
+      <c r="P108" s="21">
         <v>15177</v>
       </c>
     </row>
@@ -12426,10 +12436,10 @@
       <c r="M109" s="6">
         <v>148.3783181818182</v>
       </c>
-      <c r="O109" s="20">
+      <c r="O109" s="21">
         <v>14339</v>
       </c>
-      <c r="P109" s="20">
+      <c r="P109" s="21">
         <v>14657.40909090909</v>
       </c>
     </row>
@@ -12480,10 +12490,10 @@
       <c r="M110" s="6">
         <v>138.63090476190479</v>
       </c>
-      <c r="O110" s="20">
+      <c r="O110" s="21">
         <v>14481</v>
       </c>
-      <c r="P110" s="20">
+      <c r="P110" s="21">
         <v>14501.666666666666</v>
       </c>
     </row>
@@ -12534,10 +12544,10 @@
       <c r="M111" s="6">
         <v>127.13008695652169</v>
       </c>
-      <c r="O111" s="20">
+      <c r="O111" s="21">
         <v>14072</v>
       </c>
-      <c r="P111" s="20">
+      <c r="P111" s="21">
         <v>14168.08695652174</v>
       </c>
     </row>
@@ -12588,10 +12598,10 @@
       <c r="M112" s="6">
         <v>110.50135</v>
       </c>
-      <c r="O112" s="20">
+      <c r="O112" s="21">
         <v>14062</v>
       </c>
-      <c r="P112" s="20">
+      <c r="P112" s="21">
         <v>14030.85</v>
       </c>
     </row>
@@ -12642,10 +12652,10 @@
       <c r="M113" s="6">
         <v>91.132571428571424</v>
       </c>
-      <c r="O113" s="20">
+      <c r="O113" s="21">
         <v>14244</v>
       </c>
-      <c r="P113" s="20">
+      <c r="P113" s="21">
         <v>14206.761904761905</v>
       </c>
     </row>
@@ -12696,10 +12706,10 @@
       <c r="M114" s="6">
         <v>95.089272727272743</v>
       </c>
-      <c r="O114" s="20">
+      <c r="O114" s="21">
         <v>14215</v>
       </c>
-      <c r="P114" s="20">
+      <c r="P114" s="21">
         <v>14140.681818181818</v>
       </c>
     </row>
@@ -12750,10 +12760,10 @@
       <c r="M115" s="6">
         <v>104.81430434782605</v>
       </c>
-      <c r="O115" s="20">
+      <c r="O115" s="21">
         <v>14385</v>
       </c>
-      <c r="P115" s="20">
+      <c r="P115" s="21">
         <v>14380.304347826086</v>
       </c>
     </row>
@@ -12804,10 +12814,10 @@
       <c r="M116" s="6">
         <v>104.2079</v>
       </c>
-      <c r="O116" s="20">
+      <c r="O116" s="21">
         <v>14141</v>
       </c>
-      <c r="P116" s="20">
+      <c r="P116" s="21">
         <v>14234.35</v>
       </c>
     </row>
@@ -12858,10 +12868,10 @@
       <c r="M117" s="6">
         <v>87.171434782608685</v>
       </c>
-      <c r="O117" s="20">
+      <c r="O117" s="21">
         <v>14026</v>
       </c>
-      <c r="P117" s="20">
+      <c r="P117" s="21">
         <v>14032.695652173914</v>
       </c>
     </row>
@@ -12912,10 +12922,10 @@
       <c r="M118" s="6">
         <v>92.780863636363634</v>
       </c>
-      <c r="O118" s="20">
+      <c r="O118" s="21">
         <v>14237</v>
       </c>
-      <c r="P118" s="20">
+      <c r="P118" s="21">
         <v>14235.818181818182</v>
       </c>
     </row>
@@ -12966,10 +12976,10 @@
       <c r="M119" s="6">
         <v>78.588523809523792</v>
       </c>
-      <c r="O119" s="20">
+      <c r="O119" s="21">
         <v>14174</v>
       </c>
-      <c r="P119" s="20">
+      <c r="P119" s="21">
         <v>14102.476190476191</v>
       </c>
     </row>
@@ -13020,10 +13030,10 @@
       <c r="M120" s="6">
         <v>85.160739130434791</v>
       </c>
-      <c r="O120" s="20">
+      <c r="O120" s="21">
         <v>14008</v>
       </c>
-      <c r="P120" s="20">
+      <c r="P120" s="21">
         <v>14116.260869565218</v>
       </c>
     </row>
@@ -13074,10 +13084,10 @@
       <c r="M121" s="6">
         <v>73.489999999999981</v>
       </c>
-      <c r="O121" s="20">
+      <c r="O121" s="21">
         <v>14102</v>
       </c>
-      <c r="P121" s="20">
+      <c r="P121" s="21">
         <v>14063.619047619048</v>
       </c>
     </row>
@@ -13128,10 +13138,10 @@
       <c r="M122" s="6">
         <v>69.861227272727277</v>
       </c>
-      <c r="O122" s="20">
+      <c r="O122" s="21">
         <v>13901.004999999999</v>
       </c>
-      <c r="P122" s="20">
+      <c r="P122" s="21">
         <v>14007.5</v>
       </c>
     </row>
@@ -13182,10 +13192,10 @@
       <c r="M123" s="6">
         <v>63.303434782608704</v>
       </c>
-      <c r="O123" s="20">
+      <c r="O123" s="21">
         <v>13662</v>
       </c>
-      <c r="P123" s="20">
+      <c r="P123" s="21">
         <v>13728.434782608696</v>
       </c>
     </row>
@@ -13236,10 +13246,10 @@
       <c r="M124" s="6">
         <v>64.349299999999999</v>
       </c>
-      <c r="O124" s="20">
+      <c r="O124" s="21">
         <v>14234</v>
       </c>
-      <c r="P124" s="20">
+      <c r="P124" s="21">
         <v>13775.3</v>
       </c>
     </row>
@@ -13290,10 +13300,10 @@
       <c r="M125" s="6">
         <v>180.10131818181819</v>
       </c>
-      <c r="O125" s="20">
+      <c r="O125" s="21">
         <v>16367.004999999999</v>
       </c>
-      <c r="P125" s="20">
+      <c r="P125" s="21">
         <v>15245.363636363636</v>
       </c>
     </row>
@@ -13344,10 +13354,10 @@
       <c r="M126" s="6">
         <v>223.14500000000001</v>
       </c>
-      <c r="O126" s="20">
+      <c r="O126" s="21">
         <v>15157.004999999999</v>
       </c>
-      <c r="P126" s="20">
+      <c r="P126" s="21">
         <v>15732.09090909091</v>
       </c>
     </row>
@@ -13398,10 +13408,10 @@
       <c r="M127" s="6">
         <v>194.46928571428575</v>
       </c>
-      <c r="O127" s="20">
+      <c r="O127" s="21">
         <v>14733.004999999999</v>
       </c>
-      <c r="P127" s="20">
+      <c r="P127" s="21">
         <v>14839.619047619048</v>
       </c>
     </row>
@@ -13452,10 +13462,10 @@
       <c r="M128" s="6">
         <v>131.59750000000003</v>
       </c>
-      <c r="O128" s="20">
+      <c r="O128" s="21">
         <v>14302</v>
       </c>
-      <c r="P128" s="20">
+      <c r="P128" s="21">
         <v>14127.90909090909</v>
       </c>
     </row>
@@ -13506,10 +13516,10 @@
       <c r="M129" s="6">
         <v>121.73139130434781</v>
       </c>
-      <c r="O129" s="20">
+      <c r="O129" s="21">
         <v>14653.004999999999</v>
       </c>
-      <c r="P129" s="20">
+      <c r="P129" s="21">
         <v>14535.826086956522</v>
       </c>
     </row>
@@ -13560,10 +13570,10 @@
       <c r="M130" s="6">
         <v>107.16580952380953</v>
       </c>
-      <c r="O130" s="20">
+      <c r="O130" s="21">
         <v>14554</v>
       </c>
-      <c r="P130" s="20">
+      <c r="P130" s="21">
         <v>14689.761904761905</v>
       </c>
     </row>
@@ -13614,10 +13624,10 @@
       <c r="M131" s="6">
         <v>99.105545454545435</v>
       </c>
-      <c r="O131" s="20">
+      <c r="O131" s="21">
         <v>14918</v>
       </c>
-      <c r="P131" s="20">
+      <c r="P131" s="21">
         <v>14807.681818181818</v>
       </c>
     </row>
@@ -13668,10 +13678,10 @@
       <c r="M132" s="6">
         <v>98.591772727272712</v>
       </c>
-      <c r="O132" s="20">
+      <c r="O132" s="21">
         <v>14690</v>
       </c>
-      <c r="P132" s="20">
+      <c r="P132" s="21">
         <v>14697.954545454546</v>
       </c>
     </row>
@@ -13722,10 +13732,10 @@
       <c r="M133" s="6">
         <v>83.181857142857169</v>
       </c>
-      <c r="O133" s="20">
+      <c r="O133" s="21">
         <v>14128</v>
       </c>
-      <c r="P133" s="20">
+      <c r="P133" s="21">
         <v>14201.952380952382</v>
       </c>
     </row>
@@ -13776,10 +13786,10 @@
       <c r="M134" s="6">
         <v>72.282478260869553</v>
       </c>
-      <c r="O134" s="20">
+      <c r="O134" s="21">
         <v>14105.004999999999</v>
       </c>
-      <c r="P134" s="20">
+      <c r="P134" s="21">
         <v>14125.565217391304</v>
       </c>
     </row>
@@ -13830,10 +13840,10 @@
       <c r="M135" s="6">
         <v>71.920428571428587</v>
       </c>
-      <c r="O135" s="20">
+      <c r="O135" s="21">
         <v>14084</v>
       </c>
-      <c r="P135" s="20">
+      <c r="P135" s="21">
         <v>14025.238095238095</v>
       </c>
     </row>
@@ -13884,10 +13894,10 @@
       <c r="M136" s="6">
         <v>73.425099999999972</v>
       </c>
-      <c r="O136" s="20">
+      <c r="O136" s="21">
         <v>14229.004999999999</v>
       </c>
-      <c r="P136" s="20">
+      <c r="P136" s="21">
         <v>14029.45</v>
       </c>
     </row>
@@ -13938,10 +13948,10 @@
       <c r="M137" s="6">
         <v>81.500739130434781</v>
       </c>
-      <c r="O137" s="20">
+      <c r="O137" s="21">
         <v>14572</v>
       </c>
-      <c r="P137" s="20">
+      <c r="P137" s="21">
         <v>14388.217391304348</v>
       </c>
     </row>
@@ -13992,10 +14002,10 @@
       <c r="M138" s="6">
         <v>81.62054545454545</v>
       </c>
-      <c r="O138" s="20">
+      <c r="O138" s="21">
         <v>14468</v>
       </c>
-      <c r="P138" s="20">
+      <c r="P138" s="21">
         <v>14528.818181818182</v>
       </c>
     </row>
@@ -14046,10 +14056,10 @@
       <c r="M139" s="6">
         <v>77.338285714285703</v>
       </c>
-      <c r="O139" s="20">
+      <c r="O139" s="21">
         <v>14310</v>
       </c>
-      <c r="P139" s="20">
+      <c r="P139" s="21">
         <v>14302.333333333334</v>
       </c>
     </row>
@@ -14100,10 +14110,10 @@
       <c r="M140" s="6">
         <v>74.441090909090903</v>
       </c>
-      <c r="O140" s="20">
+      <c r="O140" s="21">
         <v>14496</v>
       </c>
-      <c r="P140" s="20">
+      <c r="P140" s="21">
         <v>14332.045454545454</v>
       </c>
     </row>
@@ -14154,10 +14164,10 @@
       <c r="M141" s="6">
         <v>78.36490909090908</v>
       </c>
-      <c r="O141" s="20">
+      <c r="O141" s="21">
         <v>14491.004999999999</v>
       </c>
-      <c r="P141" s="20">
+      <c r="P141" s="21">
         <v>14495.545454545454</v>
       </c>
     </row>
@@ -14208,10 +14218,10 @@
       <c r="M142" s="6">
         <v>75.069454545454562</v>
       </c>
-      <c r="O142" s="20">
+      <c r="O142" s="21">
         <v>14374</v>
       </c>
-      <c r="P142" s="20">
+      <c r="P142" s="21">
         <v>14378.5</v>
       </c>
     </row>
@@ -14262,10 +14272,10 @@
       <c r="M143" s="6">
         <v>72.857454545454544</v>
       </c>
-      <c r="O143" s="20">
+      <c r="O143" s="21">
         <v>14307.004999999999</v>
       </c>
-      <c r="P143" s="20">
+      <c r="P143" s="21">
         <v>14251.863636363636</v>
       </c>
     </row>
@@ -14316,10 +14326,10 @@
       <c r="M144" s="6">
         <v>85.395809523809532</v>
       </c>
-      <c r="O144" s="20">
+      <c r="O144" s="21">
         <v>14199.004999999999</v>
       </c>
-      <c r="P144" s="20">
+      <c r="P144" s="21">
         <v>14175.761904761905</v>
       </c>
     </row>
@@ -14370,10 +14380,10 @@
       <c r="M145" s="6">
         <v>82.386590909090899</v>
       </c>
-      <c r="O145" s="20">
+      <c r="O145" s="21">
         <v>14340</v>
       </c>
-      <c r="P145" s="20">
+      <c r="P145" s="21">
         <v>14265.59090909091</v>
       </c>
     </row>
@@ -14424,10 +14434,10 @@
       <c r="M146" s="6">
         <v>78.842869565217384</v>
       </c>
-      <c r="O146" s="20">
+      <c r="O146" s="21">
         <v>14269.004999999999</v>
       </c>
-      <c r="P146" s="20">
+      <c r="P146" s="21">
         <v>14322.521739130434</v>
       </c>
     </row>
@@ -14478,10 +14488,10 @@
       <c r="M147" s="6">
         <v>83.264285714285705</v>
       </c>
-      <c r="O147" s="20">
+      <c r="O147" s="21">
         <v>14381.004999999999</v>
       </c>
-      <c r="P147" s="20">
+      <c r="P147" s="21">
         <v>14338</v>
       </c>
     </row>
@@ -14532,10 +14542,10 @@
       <c r="M148" s="6">
         <v>96.822449999999989</v>
       </c>
-      <c r="O148" s="20">
+      <c r="O148" s="21">
         <v>14371.004999999999</v>
       </c>
-      <c r="P148" s="20">
+      <c r="P148" s="21">
         <v>14351.35</v>
       </c>
     </row>
@@ -14586,10 +14596,10 @@
       <c r="M149" s="6">
         <v>103.39260869565216</v>
       </c>
-      <c r="O149" s="20">
+      <c r="O149" s="21">
         <v>14349.004999999999</v>
       </c>
-      <c r="P149" s="20">
+      <c r="P149" s="21">
         <v>14349.04347826087</v>
       </c>
     </row>
@@ -14640,10 +14650,10 @@
       <c r="M150" s="6">
         <v>89.791095238095252</v>
       </c>
-      <c r="O150" s="20">
+      <c r="O150" s="21">
         <v>14418</v>
       </c>
-      <c r="P150" s="20">
+      <c r="P150" s="21">
         <v>14379.428571428571</v>
       </c>
     </row>
@@ -14694,10 +14704,10 @@
       <c r="M151" s="6">
         <v>104.3930909090909</v>
       </c>
-      <c r="O151" s="20">
+      <c r="O151" s="21">
         <v>14544</v>
       </c>
-      <c r="P151" s="20">
+      <c r="P151" s="21">
         <v>14591.818181818182</v>
       </c>
     </row>
@@ -14748,10 +14758,10 @@
       <c r="M152" s="6">
         <v>106.59518181818179</v>
       </c>
-      <c r="O152" s="20">
+      <c r="O152" s="21">
         <v>14848</v>
       </c>
-      <c r="P152" s="20">
+      <c r="P152" s="21">
         <v>14696.318181818182</v>
       </c>
     </row>
@@ -14802,10 +14812,10 @@
       <c r="M153" s="6">
         <v>140.79195238095241</v>
       </c>
-      <c r="O153" s="20">
+      <c r="O153" s="21">
         <v>14958</v>
       </c>
-      <c r="P153" s="20">
+      <c r="P153" s="21">
         <v>14979.571428571429</v>
       </c>
     </row>
@@ -14856,10 +14866,10 @@
       <c r="M154" s="6">
         <v>104.94126086956521</v>
       </c>
-      <c r="O154" s="20">
+      <c r="O154" s="21">
         <v>14875.004999999999</v>
       </c>
-      <c r="P154" s="20">
+      <c r="P154" s="21">
         <v>14838.782608695652</v>
       </c>
     </row>
@@ -14910,10 +14920,10 @@
       <c r="M155" s="6">
         <v>128.09490909090908</v>
       </c>
-      <c r="O155" s="20">
+      <c r="O155" s="21">
         <v>15247</v>
       </c>
-      <c r="P155" s="20">
+      <c r="P155" s="21">
         <v>14985.863636363636</v>
       </c>
     </row>
@@ -14964,10 +14974,10 @@
       <c r="M156" s="6">
         <v>153.26790476190476</v>
       </c>
-      <c r="O156" s="20">
+      <c r="O156" s="21">
         <v>15542</v>
       </c>
-      <c r="P156" s="20">
+      <c r="P156" s="21">
         <v>15435.904761904761</v>
       </c>
     </row>
@@ -15018,10 +15028,10 @@
       <c r="M157" s="6">
         <v>113.66349999999998</v>
       </c>
-      <c r="O157" s="20">
+      <c r="O157" s="21">
         <v>15737</v>
       </c>
-      <c r="P157" s="20">
+      <c r="P157" s="21">
         <v>15663.954545454546</v>
       </c>
     </row>
@@ -15072,10 +15082,10 @@
       <c r="M158" s="6">
         <v>98.854909090909118</v>
       </c>
-      <c r="O158" s="20">
+      <c r="O158" s="21">
         <v>15731</v>
       </c>
-      <c r="P158" s="20">
+      <c r="P158" s="21">
         <v>15600.363636363636</v>
       </c>
     </row>
@@ -15126,10 +15136,10 @@
       <c r="M159" s="6">
         <v>90.202136363636342</v>
       </c>
-      <c r="O159" s="20">
+      <c r="O159" s="21">
         <v>14979</v>
       </c>
-      <c r="P159" s="20">
+      <c r="P159" s="21">
         <v>15245.954545454546</v>
       </c>
     </row>
@@ -15180,10 +15190,10 @@
       <c r="M160" s="6">
         <v>90.466800000000006</v>
       </c>
-      <c r="O160" s="20">
+      <c r="O160" s="21">
         <v>15274</v>
       </c>
-      <c r="P160" s="20">
+      <c r="P160" s="21">
         <v>15134.05</v>
       </c>
     </row>
@@ -15234,10 +15244,10 @@
       <c r="M161" s="6">
         <v>102.52921739130434</v>
       </c>
-      <c r="O161" s="20">
+      <c r="O161" s="21">
         <v>15062</v>
       </c>
-      <c r="P161" s="20">
+      <c r="P161" s="21">
         <v>15283.217391304348</v>
       </c>
     </row>
@@ -15288,10 +15298,10 @@
       <c r="M162" s="6">
         <v>93.353300000000004</v>
       </c>
-      <c r="O162" s="20">
+      <c r="O162" s="21">
         <v>14751</v>
       </c>
-      <c r="P162" s="20">
+      <c r="P162" s="21">
         <v>14840.15</v>
       </c>
     </row>
@@ -15342,10 +15352,10 @@
       <c r="M163" s="6">
         <v>94.360217391304346</v>
       </c>
-      <c r="O163" s="20">
+      <c r="O163" s="21">
         <v>14969</v>
       </c>
-      <c r="P163" s="20">
+      <c r="P163" s="21">
         <v>14819.434782608696</v>
       </c>
     </row>
@@ -15396,10 +15406,10 @@
       <c r="M164" s="6">
         <v>85.735772727272717</v>
       </c>
-      <c r="O164" s="20">
+      <c r="O164" s="21">
         <v>15026</v>
       </c>
-      <c r="P164" s="20">
+      <c r="P164" s="21">
         <v>14941.59090909091</v>
       </c>
     </row>
@@ -15450,10 +15460,10 @@
       <c r="M165" s="6">
         <v>81.811285714285717</v>
       </c>
-      <c r="O165" s="20">
+      <c r="O165" s="21">
         <v>15083</v>
       </c>
-      <c r="P165" s="20">
+      <c r="P165" s="21">
         <v>15036.619047619048</v>
       </c>
     </row>
@@ -15504,10 +15514,10 @@
       <c r="M166" s="6">
         <v>83.005304347826069</v>
       </c>
-      <c r="O166" s="20">
+      <c r="O166" s="21">
         <v>15239</v>
       </c>
-      <c r="P166" s="20">
+      <c r="P166" s="21">
         <v>15245.217391304348</v>
       </c>
     </row>
@@ -15558,10 +15568,10 @@
       <c r="M167" s="6">
         <v>83.577380952380949</v>
       </c>
-      <c r="O167" s="20">
+      <c r="O167" s="21">
         <v>15526</v>
       </c>
-      <c r="P167" s="20">
+      <c r="P167" s="21">
         <v>15366.666666666666</v>
       </c>
     </row>
@@ -15612,10 +15622,10 @@
       <c r="M168" s="6">
         <v>98.448727272727268</v>
       </c>
-      <c r="O168" s="20">
+      <c r="O168" s="21">
         <v>15916</v>
       </c>
-      <c r="P168" s="20">
+      <c r="P168" s="21">
         <v>15754.681818181818</v>
       </c>
     </row>
@@ -15666,10 +15676,10 @@
       <c r="M169" s="6">
         <v>80.58750000000002</v>
       </c>
-      <c r="O169" s="20">
+      <c r="O169" s="21">
         <v>15384</v>
       </c>
-      <c r="P169" s="20">
+      <c r="P169" s="21">
         <v>15594.136363636364</v>
       </c>
     </row>
@@ -15720,10 +15730,10 @@
       <c r="M170" s="6">
         <v>72.753285714285695</v>
       </c>
-      <c r="O170" s="20">
+      <c r="O170" s="21">
         <v>15416</v>
       </c>
-      <c r="P170" s="20">
+      <c r="P170" s="21">
         <v>15504.476190476191</v>
       </c>
     </row>
@@ -15774,10 +15784,10 @@
       <c r="M171" s="6">
         <v>74.998478260869575</v>
       </c>
-      <c r="O171" s="20">
+      <c r="O171" s="21">
         <v>15796</v>
       </c>
-      <c r="P171" s="20">
+      <c r="P171" s="21">
         <v>15612.04347826087</v>
       </c>
     </row>
@@ -15828,10 +15838,10 @@
       <c r="M172" s="6">
         <v>72.257095238095232</v>
       </c>
-      <c r="O172" s="20">
+      <c r="O172" s="21">
         <v>15673</v>
       </c>
-      <c r="P172" s="20">
+      <c r="P172" s="21">
         <v>15646.095238095239</v>
       </c>
     </row>
@@ -15882,10 +15892,10 @@
       <c r="M173" s="6">
         <v>70.242666666666665</v>
       </c>
-      <c r="O173" s="20">
+      <c r="O173" s="21">
         <v>15853</v>
       </c>
-      <c r="P173" s="20">
+      <c r="P173" s="21">
         <v>15704.761904761905</v>
       </c>
     </row>
@@ -15936,10 +15946,10 @@
       <c r="M174" s="6">
         <v>76.358227272727262</v>
       </c>
-      <c r="O174" s="20">
+      <c r="O174" s="21">
         <v>16249</v>
       </c>
-      <c r="P174" s="20">
+      <c r="P174" s="21">
         <v>16039.181818181818</v>
       </c>
     </row>
@@ -15990,10 +16000,10 @@
       <c r="M175" s="6">
         <v>71.828565217391315</v>
       </c>
-      <c r="O175" s="20">
+      <c r="O175" s="21">
         <v>16253</v>
       </c>
-      <c r="P175" s="20">
+      <c r="P175" s="21">
         <v>16069.739130434782</v>
       </c>
     </row>
@@ -16044,10 +16054,10 @@
       <c r="M176" s="6">
         <v>75.124750000000006</v>
       </c>
-      <c r="O176" s="20">
+      <c r="O176" s="21">
         <v>16421</v>
       </c>
-      <c r="P176" s="20">
+      <c r="P176" s="21">
         <v>16335.85</v>
       </c>
     </row>
@@ -16098,10 +16108,10 @@
       <c r="M177" s="6">
         <v>74.01926086956523</v>
       </c>
-      <c r="O177" s="20">
+      <c r="O177" s="21">
         <v>16320</v>
       </c>
-      <c r="P177" s="20">
+      <c r="P177" s="21">
         <v>16243.260869565218</v>
       </c>
     </row>
@@ -16152,10 +16162,10 @@
       <c r="M178" s="6">
         <v>73.582590909090911</v>
       </c>
-      <c r="O178" s="20">
+      <c r="O178" s="21">
         <v>15409</v>
       </c>
-      <c r="P178" s="20">
+      <c r="P178" s="21">
         <v>15739.727272727272</v>
       </c>
     </row>
@@ -16206,10 +16216,10 @@
       <c r="M179" s="6">
         <v>69.288714285714278</v>
       </c>
-      <c r="O179" s="20">
+      <c r="O179" s="21">
         <v>15138</v>
       </c>
-      <c r="P179" s="20">
+      <c r="P179" s="21">
         <v>15323.904761904761</v>
       </c>
     </row>
@@ -16260,10 +16270,10 @@
       <c r="M180" s="6">
         <v>68.92404347826087</v>
       </c>
-      <c r="O180" s="20">
+      <c r="O180" s="21">
         <v>15732</v>
       </c>
-      <c r="P180" s="20">
+      <c r="P180" s="21">
         <v>15563.217391304348</v>
       </c>
     </row>
@@ -16314,10 +16324,10 @@
       <c r="M181" s="6">
         <v>72.635238095238094</v>
       </c>
-      <c r="O181" s="20">
+      <c r="O181" s="21">
         <v>15864</v>
       </c>
-      <c r="P181" s="20">
+      <c r="P181" s="21">
         <v>15818</v>
       </c>
     </row>
@@ -16368,10 +16378,10 @@
       <c r="M182" s="6">
         <v>74.619590909090917</v>
       </c>
-      <c r="O182" s="20">
+      <c r="O182" s="21">
         <v>16162</v>
       </c>
-      <c r="P182" s="20">
+      <c r="P182" s="21">
         <v>16041.681818181818</v>
       </c>
     </row>
@@ -16422,10 +16432,10 @@
       <c r="M183" s="6">
         <v>77.286695652173904</v>
       </c>
-      <c r="O183" s="20">
+      <c r="O183" s="21">
         <v>16259</v>
       </c>
-      <c r="P183" s="20">
+      <c r="P183" s="21">
         <v>16238.695652173914</v>
       </c>
     </row>
@@ -16476,10 +16486,10 @@
       <c r="M184" s="6">
         <v>73.931150000000002</v>
       </c>
-      <c r="O184" s="20">
+      <c r="O184" s="21">
         <v>16430.994999999999</v>
       </c>
-      <c r="P184" s="20">
+      <c r="P184" s="21">
         <v>16342.35</v>
       </c>
     </row>
@@ -16530,10 +16540,10 @@
       <c r="M185" s="6">
         <v>84.90695238095239</v>
       </c>
-      <c r="O185" s="20">
+      <c r="O185" s="21">
         <v>16588</v>
       </c>
-      <c r="P185" s="20">
+      <c r="P185" s="21">
         <v>16455.380952380954</v>
       </c>
     </row>
@@ -16584,10 +16594,10 @@
       <c r="M186" s="6">
         <v>107.06404545454544</v>
       </c>
-      <c r="O186" s="20">
+      <c r="O186" s="21">
         <v>16787</v>
       </c>
-      <c r="P186" s="20">
+      <c r="P186" s="21">
         <v>16756.045454545456</v>
       </c>
     </row>
@@ -16638,10 +16648,10 @@
       <c r="M187" s="6">
         <v>86.467818181818174</v>
       </c>
-      <c r="O187" s="20">
+      <c r="O187" s="21">
         <v>16255</v>
       </c>
-      <c r="P187" s="20">
+      <c r="P187" s="21">
         <v>16417.136363636364</v>
       </c>
     </row>
@@ -16692,10 +16702,10 @@
       <c r="M188" s="6">
         <v>78.105571428571452</v>
       </c>
-      <c r="O188" s="20">
+      <c r="O188" s="21">
         <v>16233</v>
       </c>
-      <c r="P188" s="20">
+      <c r="P188" s="21">
         <v>16291.142857142857</v>
       </c>
     </row>
@@ -16746,10 +16756,10 @@
       <c r="M189" s="6">
         <v>73.85108695652174</v>
       </c>
-      <c r="O189" s="20">
+      <c r="O189" s="21">
         <v>16387.005000000001</v>
       </c>
-      <c r="P189" s="20">
+      <c r="P189" s="21">
         <v>16280.130434782608</v>
       </c>
     </row>
@@ -16800,10 +16810,10 @@
       <c r="M190" s="6">
         <v>70.2942380952381</v>
       </c>
-      <c r="O190" s="20">
+      <c r="O190" s="21">
         <v>16356</v>
       </c>
-      <c r="P190" s="20">
+      <c r="P190" s="21">
         <v>16299.238095238095</v>
       </c>
     </row>
@@ -16854,10 +16864,10 @@
       <c r="M191" s="6">
         <v>73.98981818181818</v>
       </c>
-      <c r="O191" s="20">
+      <c r="O191" s="21">
         <v>16680</v>
       </c>
-      <c r="P191" s="20">
+      <c r="P191" s="21">
         <v>16514.136363636364</v>
       </c>
     </row>
@@ -16909,10 +16919,10 @@
       <c r="M192" s="6">
         <v>79.221956521739116</v>
       </c>
-      <c r="O192" s="20">
+      <c r="O192" s="21">
         <v>16640</v>
       </c>
-      <c r="P192" s="20">
+      <c r="P192" s="21">
         <v>16583.130434782608</v>
       </c>
     </row>
@@ -16963,10 +16973,10 @@
       <c r="M193" s="6">
         <v>75.448200000000014</v>
       </c>
-      <c r="O193" s="20">
+      <c r="O193" s="21">
         <v>16644</v>
       </c>
-      <c r="P193" s="20">
+      <c r="P193" s="21">
         <v>16692.45</v>
       </c>
     </row>
@@ -17017,10 +17027,10 @@
       <c r="M194" s="6">
         <v>71.1198695652174</v>
       </c>
-      <c r="O194" s="20">
+      <c r="O194" s="21">
         <v>16782</v>
       </c>
-      <c r="P194" s="20">
+      <c r="P194" s="21">
         <v>16702.217391304348</v>
       </c>
     </row>
@@ -17044,19 +17054,19 @@
       </c>
       <c r="F195" s="5">
         <f>Sheet3!D211/Sheet3!C211</f>
-        <v>0.39399006826234167</v>
+        <v>0.39399006824013183</v>
       </c>
       <c r="G195" s="5">
         <f>Sheet3!E211/Sheet3!F211</f>
-        <v>0.92702447246165531</v>
+        <v>0.92702447247400843</v>
       </c>
       <c r="H195" s="6">
         <f t="shared" si="10"/>
-        <v>0.4250050348898835</v>
+        <v>0.42500503486026187</v>
       </c>
       <c r="I195" s="6">
         <f>LN(Sheet3!B211)</f>
-        <v>14.581624232904288</v>
+        <v>14.581624232764844</v>
       </c>
       <c r="J195" s="5">
         <v>4.75</v>
@@ -17071,10 +17081,10 @@
       <c r="M195" s="6">
         <v>72.201045454545451</v>
       </c>
-      <c r="O195" s="20">
+      <c r="O195" s="21">
         <v>16786</v>
       </c>
-      <c r="P195" s="20">
+      <c r="P195" s="21">
         <v>16814.863636363636</v>
       </c>
     </row>
@@ -17083,7 +17093,7 @@
         <v>46054</v>
       </c>
       <c r="B196" s="7">
-        <f t="shared" ref="B196:B200" si="12">O196</f>
+        <f t="shared" ref="B196:B203" si="12">O196</f>
         <v>16758</v>
       </c>
       <c r="C196" s="5">
@@ -17093,24 +17103,24 @@
         <v>2.4724599999999999</v>
       </c>
       <c r="E196" s="8">
-        <f t="shared" ref="E196:E200" si="13">C196-D196</f>
+        <f t="shared" ref="E196:E203" si="13">C196-D196</f>
         <v>0.16135477999999992</v>
       </c>
       <c r="F196" s="5">
         <f>Sheet3!D212/Sheet3!C212</f>
-        <v>0.42134055259983449</v>
+        <v>0.42134055259190589</v>
       </c>
       <c r="G196" s="5">
         <f>Sheet3!E212/Sheet3!F212</f>
-        <v>0.9422382737979208</v>
+        <v>0.94223827383482428</v>
       </c>
       <c r="H196" s="6">
         <f t="shared" ref="H196:H197" si="14">F196/G196</f>
-        <v>0.44716985535040815</v>
+        <v>0.44716985532447973</v>
       </c>
       <c r="I196" s="6">
         <f>LN(Sheet3!B212)</f>
-        <v>14.554431515587812</v>
+        <v>14.554431515348996</v>
       </c>
       <c r="J196" s="5">
         <v>4.75</v>
@@ -17119,16 +17129,16 @@
         <v>3.64</v>
       </c>
       <c r="L196" s="8">
-        <f t="shared" ref="L196:L200" si="15">J196-K196</f>
+        <f t="shared" ref="L196:L203" si="15">J196-K196</f>
         <v>1.1099999999999999</v>
       </c>
       <c r="M196" s="6">
         <v>80.089349999999996</v>
       </c>
-      <c r="O196" s="20">
+      <c r="O196" s="21">
         <v>16758</v>
       </c>
-      <c r="P196" s="20">
+      <c r="P196" s="21">
         <v>16815.349999999999</v>
       </c>
     </row>
@@ -17152,19 +17162,19 @@
       </c>
       <c r="F197" s="5">
         <f>Sheet3!D213/Sheet3!C213</f>
-        <v>0.41799486233442684</v>
+        <v>0.41799463824510774</v>
       </c>
       <c r="G197" s="5">
         <f>Sheet3!E213/Sheet3!F213</f>
-        <v>1.1021862589413383</v>
+        <v>1.1021862589539637</v>
       </c>
       <c r="H197" s="6">
         <f t="shared" si="14"/>
-        <v>0.37924158366473865</v>
+        <v>0.37924138034691884</v>
       </c>
       <c r="I197" s="6">
         <f>LN(Sheet3!B213)</f>
-        <v>14.558504757834987</v>
+        <v>14.558504648664705</v>
       </c>
       <c r="J197" s="5">
         <v>4.75</v>
@@ -17179,10 +17189,10 @@
       <c r="M197" s="6">
         <v>93.77709090909093</v>
       </c>
-      <c r="O197" s="20">
+      <c r="O197" s="21">
         <v>16993</v>
       </c>
-      <c r="P197" s="20">
+      <c r="P197" s="21">
         <v>16935.045454545456</v>
       </c>
     </row>
@@ -17206,19 +17216,19 @@
       </c>
       <c r="F198" s="5">
         <f>Sheet3!D214/Sheet3!C214</f>
-        <v>0.47080132286428161</v>
+        <v>0.47080141450780549</v>
       </c>
       <c r="G198" s="5">
         <f>Sheet3!E214/Sheet3!F214</f>
-        <v>1.0469816529278275</v>
+        <v>1.0469816529078959</v>
       </c>
       <c r="H198" s="6">
         <f>F198/G198</f>
-        <v>0.44967485490095382</v>
+        <v>0.4496749424406794</v>
       </c>
       <c r="I198" s="6">
         <f>LN(Sheet3!B214)</f>
-        <v>14.534569120308721</v>
+        <v>14.53456574198389</v>
       </c>
       <c r="J198" s="5">
         <v>4.75</v>
@@ -17233,10 +17243,10 @@
       <c r="M198" s="6">
         <v>88.659409090909108</v>
       </c>
-      <c r="O198" s="20">
+      <c r="O198" s="21">
         <v>17324</v>
       </c>
-      <c r="P198" s="20">
+      <c r="P198" s="21">
         <v>17138.590909090908</v>
       </c>
     </row>
@@ -17260,19 +17270,19 @@
       </c>
       <c r="F199" s="5">
         <f>Sheet3!D215/Sheet3!C215</f>
-        <v>0.42408491974896417</v>
+        <v>0.42408485687963365</v>
       </c>
       <c r="G199" s="5">
         <f>Sheet3!E215/Sheet3!F215</f>
-        <v>0.90346575933060791</v>
+        <v>0.90346575932369</v>
       </c>
       <c r="H199" s="6">
         <f>F199/G199</f>
-        <v>0.46939788848575226</v>
+        <v>0.46939781890250282</v>
       </c>
       <c r="I199" s="6">
         <f>LN(Sheet3!B215)</f>
-        <v>14.536806380218714</v>
+        <v>14.536409496568682</v>
       </c>
       <c r="J199" s="5">
         <v>5.25</v>
@@ -17287,10 +17297,10 @@
       <c r="M199" s="6">
         <v>88.392947368421048</v>
       </c>
-      <c r="O199" s="20">
+      <c r="O199" s="21">
         <v>17789</v>
       </c>
-      <c r="P199" s="20">
+      <c r="P199" s="21">
         <v>17542.315789473683</v>
       </c>
     </row>
@@ -17302,31 +17312,31 @@
         <f t="shared" si="12"/>
         <v>17962</v>
       </c>
-      <c r="C200" s="21">
+      <c r="C200" s="22">
         <v>2.76</v>
       </c>
-      <c r="D200" s="12">
-        <v>2.9</v>
-      </c>
-      <c r="E200" s="1">
+      <c r="D200" s="22">
+        <v>2.6</v>
+      </c>
+      <c r="E200" s="8">
         <f t="shared" si="13"/>
-        <v>-0.14000000000000012</v>
+        <v>0.1599999999999997</v>
       </c>
       <c r="F200" s="5">
         <f>Sheet3!D216/Sheet3!C216</f>
-        <v>0.4504062402856282</v>
+        <v>0.45040660525449988</v>
       </c>
       <c r="G200" s="5">
         <f>Sheet3!E216/Sheet3!F216</f>
-        <v>0.96480833123137733</v>
-      </c>
-      <c r="H200" s="14">
-        <f>F200/G200</f>
-        <v>0.46683494089523275</v>
-      </c>
-      <c r="I200" s="14">
+        <v>0.96480948232521935</v>
+      </c>
+      <c r="H200" s="6">
+        <f t="shared" ref="H200:H203" si="16">F200/G200</f>
+        <v>0.46683476220507975</v>
+      </c>
+      <c r="I200" s="6">
         <f>LN(Sheet3!B216)</f>
-        <v>14.546148134792231</v>
+        <v>14.4581405582506</v>
       </c>
       <c r="J200" s="5">
         <v>5.75</v>
@@ -17341,11 +17351,174 @@
       <c r="M200" s="6">
         <v>89.87</v>
       </c>
-      <c r="O200" s="20">
+      <c r="O200" s="21">
         <v>17962</v>
       </c>
-      <c r="P200" s="20">
+      <c r="P200" s="21">
         <v>17905.5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16" x14ac:dyDescent="0.75">
+      <c r="A201" s="4">
+        <v>46204</v>
+      </c>
+      <c r="B201" s="7">
+        <f t="shared" si="12"/>
+        <v>18058</v>
+      </c>
+      <c r="C201" s="22">
+        <v>2.76</v>
+      </c>
+      <c r="D201" s="22">
+        <v>2.5</v>
+      </c>
+      <c r="E201" s="8">
+        <f t="shared" si="13"/>
+        <v>0.25999999999999979</v>
+      </c>
+      <c r="F201" s="5">
+        <f>Sheet3!D217/Sheet3!C217</f>
+        <v>0.47315045745650575</v>
+      </c>
+      <c r="G201" s="5">
+        <f>Sheet3!E217/Sheet3!F217</f>
+        <v>0.99519963830678149</v>
+      </c>
+      <c r="H201" s="6">
+        <f t="shared" si="16"/>
+        <v>0.47543270640805013</v>
+      </c>
+      <c r="I201" s="6">
+        <f>LN(Sheet3!B217)</f>
+        <v>14.44803436908825</v>
+      </c>
+      <c r="J201" s="5">
+        <v>5.75</v>
+      </c>
+      <c r="K201">
+        <v>3.63</v>
+      </c>
+      <c r="L201" s="8">
+        <f t="shared" si="15"/>
+        <v>2.12</v>
+      </c>
+      <c r="M201" s="1">
+        <v>93.36</v>
+      </c>
+      <c r="O201" s="24">
+        <v>18058</v>
+      </c>
+      <c r="P201" s="24">
+        <v>18014.478260869564</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16" x14ac:dyDescent="0.75">
+      <c r="A202" s="4">
+        <v>46235</v>
+      </c>
+      <c r="B202" s="7">
+        <f t="shared" si="12"/>
+        <v>17746</v>
+      </c>
+      <c r="C202" s="22">
+        <v>2.92</v>
+      </c>
+      <c r="D202" s="22">
+        <v>2.4</v>
+      </c>
+      <c r="E202" s="8">
+        <f t="shared" si="13"/>
+        <v>0.52</v>
+      </c>
+      <c r="F202" s="12">
+        <f>Sheet3!D218/Sheet3!C218</f>
+        <v>0.30374423783793852</v>
+      </c>
+      <c r="G202" s="12">
+        <f>Sheet3!E218/Sheet3!F218</f>
+        <v>0.90384588523585718</v>
+      </c>
+      <c r="H202" s="14">
+        <f t="shared" si="16"/>
+        <v>0.33605755450076197</v>
+      </c>
+      <c r="I202" s="14">
+        <f>LN(Sheet3!B218)</f>
+        <v>14.439324995182591</v>
+      </c>
+      <c r="J202" s="5">
+        <v>5.75</v>
+      </c>
+      <c r="K202">
+        <v>3.63</v>
+      </c>
+      <c r="L202" s="8">
+        <f t="shared" si="15"/>
+        <v>2.12</v>
+      </c>
+      <c r="M202" s="1">
+        <v>84.57</v>
+      </c>
+      <c r="O202" s="24">
+        <v>17746</v>
+      </c>
+      <c r="P202" s="24">
+        <v>17832.894736842107</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16" x14ac:dyDescent="0.75">
+      <c r="A203" s="4">
+        <v>46266</v>
+      </c>
+      <c r="B203" s="7">
+        <f t="shared" si="12"/>
+        <v>17877</v>
+      </c>
+      <c r="C203" s="12">
+        <v>3.1</v>
+      </c>
+      <c r="D203" s="12">
+        <v>2.5</v>
+      </c>
+      <c r="E203" s="8">
+        <f t="shared" si="13"/>
+        <v>0.60000000000000009</v>
+      </c>
+      <c r="F203" s="12">
+        <f>Sheet3!D219/Sheet3!C219</f>
+        <v>0.51840951390246481</v>
+      </c>
+      <c r="G203" s="12">
+        <f>Sheet3!E219/Sheet3!F219</f>
+        <v>0.98486160545836199</v>
+      </c>
+      <c r="H203" s="14">
+        <f t="shared" si="16"/>
+        <v>0.52637803223245072</v>
+      </c>
+      <c r="I203" s="14">
+        <f>LN(Sheet3!B219)</f>
+        <v>14.447930308444844</v>
+      </c>
+      <c r="J203" s="5">
+        <v>5.75</v>
+      </c>
+      <c r="K203">
+        <f>K202+0.25</f>
+        <v>3.88</v>
+      </c>
+      <c r="L203" s="8">
+        <f t="shared" si="15"/>
+        <v>1.87</v>
+      </c>
+      <c r="M203" s="1">
+        <v>91.19</v>
+      </c>
+      <c r="O203" s="24">
+        <v>17877</v>
+      </c>
+      <c r="P203" s="24">
+        <v>17749</v>
       </c>
     </row>
   </sheetData>
@@ -17359,7 +17532,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18DB994A-7F05-44A4-BABA-58A6A22D0008}">
-  <dimension ref="A1:Q217"/>
+  <dimension ref="A1:Q219"/>
   <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
   <cols>
     <col min="1" max="1" width="12.58984375" customWidth="1"/>
@@ -21807,28 +21980,28 @@
       <c r="A211" s="9">
         <v>46023</v>
       </c>
-      <c r="B211" s="5">
-        <v>2151388.9890000001</v>
-      </c>
-      <c r="C211" s="19">
-        <v>56234.158636829998</v>
-      </c>
-      <c r="D211" s="19">
+      <c r="B211" s="22">
+        <v>2151388.9887000001</v>
+      </c>
+      <c r="C211" s="5">
+        <v>56234.158640000001</v>
+      </c>
+      <c r="D211" s="5">
         <v>22155.7</v>
       </c>
-      <c r="E211" s="19">
-        <v>19654.17041603</v>
-      </c>
-      <c r="F211" s="19">
-        <v>21201.350126000001</v>
+      <c r="E211" s="5">
+        <v>19654.170419999999</v>
+      </c>
+      <c r="F211" s="5">
+        <v>21201.350129999999</v>
       </c>
       <c r="J211" s="5">
         <f t="shared" si="7"/>
-        <v>5.5372700041248208</v>
+        <v>5.537269989408216</v>
       </c>
       <c r="K211" s="5">
         <f t="shared" si="8"/>
-        <v>1.7776718788036874</v>
+        <v>1.77767188454105</v>
       </c>
       <c r="L211" s="5">
         <f t="shared" si="9"/>
@@ -21836,43 +22009,43 @@
       </c>
       <c r="M211" s="5">
         <f t="shared" si="10"/>
-        <v>25.5105276596788</v>
+        <v>25.510527685031008</v>
       </c>
       <c r="N211" s="5">
         <f t="shared" si="11"/>
-        <v>18.206122350235759</v>
+        <v>18.206122372537365</v>
       </c>
       <c r="O211" s="16">
         <f t="shared" si="6"/>
-        <v>954.34987399999955</v>
+        <v>954.34987000000183</v>
       </c>
     </row>
     <row r="212" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A212" s="9">
         <v>46054</v>
       </c>
-      <c r="B212" s="5">
-        <v>2093675.1310000001</v>
-      </c>
-      <c r="C212" s="19">
-        <v>52610.174509010001</v>
-      </c>
-      <c r="D212" s="19">
+      <c r="B212" s="22">
+        <v>2093675.1305</v>
+      </c>
+      <c r="C212" s="5">
+        <v>52610.174509999997</v>
+      </c>
+      <c r="D212" s="5">
         <v>22166.799999999999</v>
       </c>
-      <c r="E212" s="19">
-        <v>19686.701605459999</v>
-      </c>
-      <c r="F212" s="19">
-        <v>20893.549066</v>
+      <c r="E212" s="5">
+        <v>19686.70161</v>
+      </c>
+      <c r="F212" s="5">
+        <v>20893.549070000001</v>
       </c>
       <c r="J212" s="5">
         <f t="shared" si="7"/>
-        <v>1.9551465617064707</v>
+        <v>1.9551465373581038</v>
       </c>
       <c r="K212" s="5">
         <f t="shared" si="8"/>
-        <v>-7.0800896430143041</v>
+        <v>-7.0800896412657579</v>
       </c>
       <c r="L212" s="5">
         <f t="shared" si="9"/>
@@ -21880,39 +22053,39 @@
       </c>
       <c r="M212" s="5">
         <f t="shared" si="10"/>
-        <v>-2.2770382174792019</v>
+        <v>-2.2770381949430458</v>
       </c>
       <c r="N212" s="5">
         <f t="shared" si="11"/>
-        <v>10.846991932664693</v>
+        <v>10.84699195388599</v>
       </c>
       <c r="O212" s="16">
         <f t="shared" si="6"/>
-        <v>1273.2509339999997</v>
+        <v>1273.2509299999983</v>
       </c>
     </row>
     <row r="213" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A213" s="9">
         <v>46082</v>
       </c>
-      <c r="B213" s="5">
-        <v>2102220.5690000001</v>
-      </c>
-      <c r="C213" s="19">
+      <c r="B213" s="22">
+        <v>2102220.3394999998</v>
+      </c>
+      <c r="C213" s="22">
         <v>53892.528425329998</v>
       </c>
-      <c r="D213" s="19">
-        <v>22526.799999999999</v>
-      </c>
-      <c r="E213" s="19">
+      <c r="D213" s="22">
+        <v>22526.787923259999</v>
+      </c>
+      <c r="E213" s="22">
         <v>21168.349918619999</v>
       </c>
-      <c r="F213" s="19">
-        <v>19205.782822000001</v>
+      <c r="F213" s="22">
+        <v>19205.782821780002</v>
       </c>
       <c r="J213" s="5">
         <f t="shared" si="7"/>
-        <v>2.7195655552345102</v>
+        <v>2.7195543413111665</v>
       </c>
       <c r="K213" s="5">
         <f t="shared" si="8"/>
@@ -21920,7 +22093,7 @@
       </c>
       <c r="L213" s="5">
         <f t="shared" si="9"/>
-        <v>-3.0991283382290788</v>
+        <v>-3.099180287313402</v>
       </c>
       <c r="M213" s="5">
         <f t="shared" si="10"/>
@@ -21928,35 +22101,36 @@
       </c>
       <c r="N213" s="5">
         <f t="shared" si="11"/>
-        <v>1.5105985501649997</v>
+        <v>1.5105985490022249</v>
       </c>
       <c r="O213" s="16">
         <f>D213-F213</f>
-        <v>3321.0171779999982</v>
+        <v>3321.0051014799974</v>
       </c>
     </row>
     <row r="214" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A214" s="9">
         <v>46113</v>
       </c>
-      <c r="B214" s="5">
-        <v>2052500</v>
-      </c>
-      <c r="C214" s="19">
+      <c r="B214" s="22">
+        <v>2052493.0660000001</v>
+      </c>
+      <c r="C214" s="22">
         <v>53744.114069310002</v>
       </c>
-      <c r="D214" s="19">
-        <v>25302.799999999999</v>
-      </c>
-      <c r="E214" s="19">
+      <c r="D214" s="22">
+        <v>25302.804925299999</v>
+      </c>
+      <c r="E214" s="22">
         <v>26398.289369419999</v>
       </c>
-      <c r="F214" s="19">
-        <v>25213.707705000001</v>
-      </c>
+      <c r="F214" s="22">
+        <v>25213.707705479999</v>
+      </c>
+      <c r="G214" s="18"/>
       <c r="J214" s="5">
         <f>B214/B202*100-100</f>
-        <v>3.6577718194443065</v>
+        <v>3.6574216304115339</v>
       </c>
       <c r="K214" s="5">
         <f t="shared" ref="K214:N217" si="12">C214/C202*100-100</f>
@@ -21964,7 +22138,7 @@
       </c>
       <c r="L214" s="5">
         <f t="shared" si="12"/>
-        <v>21.977375137728444</v>
+        <v>21.977398881154684</v>
       </c>
       <c r="M214" s="5">
         <f t="shared" si="12"/>
@@ -21972,36 +22146,36 @@
       </c>
       <c r="N214" s="5">
         <f t="shared" si="12"/>
-        <v>22.485743144447198</v>
+        <v>22.485743146778987</v>
       </c>
       <c r="O214" s="16">
         <f>D214-F214</f>
-        <v>89.092294999998558</v>
+        <v>89.097219819999737</v>
       </c>
     </row>
     <row r="215" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A215" s="9">
         <v>46143</v>
       </c>
-      <c r="B215" s="12">
-        <f>B203*(1+J215%)</f>
-        <v>2057097.1165200002</v>
-      </c>
-      <c r="C215" s="19">
+      <c r="B215" s="22">
+        <v>2056280.8503</v>
+      </c>
+      <c r="C215" s="22">
         <v>54714.277540770003</v>
       </c>
-      <c r="D215" s="19">
-        <v>23203.5</v>
-      </c>
-      <c r="E215" s="19">
+      <c r="D215" s="22">
+        <v>23203.496560150001</v>
+      </c>
+      <c r="E215" s="22">
         <v>22418.37203101</v>
       </c>
-      <c r="F215" s="19">
-        <v>24813.748390000001</v>
+      <c r="F215" s="22">
+        <v>24813.748390190001</v>
       </c>
       <c r="G215" s="18"/>
       <c r="J215" s="5">
-        <v>5.2</v>
+        <f t="shared" ref="J215:J217" si="13">B215/B203*100-100</f>
+        <v>5.1582561242955478</v>
       </c>
       <c r="K215" s="5">
         <f t="shared" si="12"/>
@@ -22009,7 +22183,7 @@
       </c>
       <c r="L215" s="5">
         <f t="shared" si="12"/>
-        <v>-5.7297159706282628</v>
+        <v>-5.729729945918038</v>
       </c>
       <c r="M215" s="5">
         <f t="shared" si="12"/>
@@ -22017,39 +22191,36 @@
       </c>
       <c r="N215" s="5">
         <f t="shared" si="12"/>
-        <v>22.161194170067233</v>
+        <v>22.161194171002634</v>
       </c>
       <c r="O215" s="16">
-        <f t="shared" ref="O215:O216" si="13">D215-F215</f>
-        <v>-1610.2483900000007</v>
-      </c>
-      <c r="P215" s="18"/>
-      <c r="Q215" s="15"/>
+        <f t="shared" ref="O215:O219" si="14">D215-F215</f>
+        <v>-1610.2518300400006</v>
+      </c>
     </row>
     <row r="216" spans="1:17" x14ac:dyDescent="0.75">
       <c r="A216" s="9">
         <v>46174</v>
       </c>
-      <c r="B216" s="12">
-        <f>B204*(1+J216%)</f>
-        <v>2076404.0528398708</v>
-      </c>
-      <c r="C216" s="19">
+      <c r="B216" s="22">
+        <v>1901475.1891999999</v>
+      </c>
+      <c r="C216" s="22">
         <v>56523.861622910001</v>
       </c>
-      <c r="D216" s="19">
-        <v>25458.7</v>
-      </c>
-      <c r="E216" s="19">
+      <c r="D216" s="22">
+        <v>25458.720629449999</v>
+      </c>
+      <c r="E216" s="22">
         <v>24997.412015540001</v>
       </c>
-      <c r="F216" s="19">
-        <v>25909.200000000001</v>
+      <c r="F216" s="22">
+        <v>25909.169088279999</v>
       </c>
       <c r="G216" s="18"/>
-      <c r="J216" s="12">
-        <f>_xlfn.FORECAST.LINEAR(J215,J204:J215,J203:J214)</f>
-        <v>5.6756715110322711</v>
+      <c r="J216" s="5">
+        <f>B216/B204*100-100</f>
+        <v>-3.2270876155078838</v>
       </c>
       <c r="K216" s="5">
         <f t="shared" si="12"/>
@@ -22057,7 +22228,7 @@
       </c>
       <c r="L216" s="5">
         <f t="shared" si="12"/>
-        <v>8.628421479316458</v>
+        <v>8.6285095020587619</v>
       </c>
       <c r="M216" s="5">
         <f t="shared" si="12"/>
@@ -22065,54 +22236,170 @@
       </c>
       <c r="N216" s="5">
         <f t="shared" si="12"/>
-        <v>34.015414058863087</v>
+        <v>34.015254167899428</v>
       </c>
       <c r="O216" s="16">
+        <f t="shared" si="14"/>
+        <v>-450.44845883000016</v>
+      </c>
+      <c r="P216" s="18"/>
+    </row>
+    <row r="217" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A217" s="9">
+        <v>46204</v>
+      </c>
+      <c r="B217" s="22">
+        <v>1882355.2986000001</v>
+      </c>
+      <c r="C217" s="25">
+        <v>55408.83082291</v>
+      </c>
+      <c r="D217" s="22">
+        <v>26216.713650990001</v>
+      </c>
+      <c r="E217" s="22">
+        <v>25969.545760649999</v>
+      </c>
+      <c r="F217" s="22">
+        <v>26094.81028835</v>
+      </c>
+      <c r="J217" s="5">
         <f t="shared" si="13"/>
-        <v>-450.5</v>
-      </c>
-      <c r="P216" s="18" t="s">
+        <v>-6.0758644186697524</v>
+      </c>
+      <c r="K217" s="5">
+        <f t="shared" si="12"/>
+        <v>-5.9274516565243118</v>
+      </c>
+      <c r="L217" s="5">
+        <f t="shared" si="12"/>
+        <v>5.9308237981890102</v>
+      </c>
+      <c r="M217" s="5">
+        <f t="shared" si="12"/>
+        <v>30.438646656122842</v>
+      </c>
+      <c r="N217" s="5">
+        <f t="shared" si="12"/>
+        <v>26.825287908619018</v>
+      </c>
+      <c r="O217" s="16">
+        <f t="shared" si="14"/>
+        <v>121.90336264000143</v>
+      </c>
+      <c r="P217" s="13"/>
+    </row>
+    <row r="218" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A218" s="9">
+        <v>46235</v>
+      </c>
+      <c r="B218" s="12">
+        <f t="shared" ref="B217:B219" si="15">B206*(1+J218%)</f>
+        <v>1866032.3470044103</v>
+      </c>
+      <c r="C218" s="20">
+        <f>C206*(1+K218%)</f>
+        <v>87609.139154100005</v>
+      </c>
+      <c r="D218" s="20">
+        <f>D206*(1+L218%)</f>
+        <v>26610.771200000003</v>
+      </c>
+      <c r="E218" s="20">
+        <f>E206*(1+M218%)</f>
+        <v>22038.42938895</v>
+      </c>
+      <c r="F218" s="20">
+        <f>F206*(1+N218%)</f>
+        <v>24382.950400000002</v>
+      </c>
+      <c r="G218" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="Q216" s="15" t="s">
+      <c r="H218" s="15" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.75">
-      <c r="B217" s="12"/>
-      <c r="G217" s="18" t="s">
+      <c r="J218" s="12">
+        <f>_xlfn.FORECAST.LINEAR(J217,J206:J217,J205:J216)</f>
+        <v>-7.8458244242880912</v>
+      </c>
+      <c r="K218" s="26">
+        <v>31.1</v>
+      </c>
+      <c r="L218" s="26">
+        <v>6.6</v>
+      </c>
+      <c r="M218" s="26">
+        <v>10.5</v>
+      </c>
+      <c r="N218" s="26">
+        <v>25.2</v>
+      </c>
+      <c r="O218" s="16">
+        <f t="shared" si="14"/>
+        <v>2227.8208000000013</v>
+      </c>
+      <c r="P218" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="H217" s="15" t="s">
+      <c r="Q218" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J217" s="12">
-        <f>_xlfn.FORECAST.LINEAR(J216,J205:J216,J204:J215)</f>
-        <v>6.1223116507551287</v>
-      </c>
-      <c r="K217" s="12">
-        <f t="shared" ref="K217:N217" si="14">_xlfn.FORECAST.LINEAR(K216,K205:K216,K204:K215)</f>
-        <v>-1.5571138801144961</v>
-      </c>
-      <c r="L217" s="12">
+    </row>
+    <row r="219" spans="1:17" x14ac:dyDescent="0.75">
+      <c r="A219" s="9">
+        <v>46266</v>
+      </c>
+      <c r="B219" s="12">
+        <f t="shared" si="15"/>
+        <v>1882159.4296878092</v>
+      </c>
+      <c r="C219" s="12">
+        <f t="shared" ref="C219" si="16">C207*(1+K219%)</f>
+        <v>49192.529845485762</v>
+      </c>
+      <c r="D219" s="12">
+        <f t="shared" ref="D219" si="17">D207*(1+L219%)</f>
+        <v>25501.875484830765</v>
+      </c>
+      <c r="E219" s="12">
+        <f t="shared" ref="E219" si="18">E207*(1+M219%)</f>
+        <v>24573.100008128149</v>
+      </c>
+      <c r="F219" s="12">
+        <f t="shared" ref="F219" si="19">F207*(1+N219%)</f>
+        <v>24950.81529418709</v>
+      </c>
+      <c r="J219" s="12">
+        <f>_xlfn.FORECAST.LINEAR(J218,J207:J218,J206:J217)</f>
+        <v>-9.7432749410273711</v>
+      </c>
+      <c r="K219" s="12">
+        <f>_xlfn.FORECAST.LINEAR(K218,K207:K218,K206:K217)</f>
+        <v>-20.843752501466625</v>
+      </c>
+      <c r="L219" s="12">
+        <f t="shared" ref="K219:L219" si="20">_xlfn.FORECAST.LINEAR(L218,L207:L218,L206:L217)</f>
+        <v>3.3338958261475011</v>
+      </c>
+      <c r="M219" s="12">
+        <f>_xlfn.FORECAST.LINEAR(M218,M207:M218,M206:M217)</f>
+        <v>15.797309505245963</v>
+      </c>
+      <c r="N219" s="12">
+        <f>_xlfn.FORECAST.LINEAR(N218,N207:N218,N206:N217)</f>
+        <v>22.697060255747839</v>
+      </c>
+      <c r="O219" s="16">
         <f t="shared" si="14"/>
-        <v>3.1638925862450153</v>
-      </c>
-      <c r="M217" s="12">
-        <f t="shared" si="14"/>
-        <v>11.807078045247842</v>
-      </c>
-      <c r="N217" s="12">
-        <f t="shared" si="14"/>
-        <v>30.147253793494126</v>
-      </c>
-      <c r="P217" s="13" t="s">
+        <v>551.06019064367501</v>
+      </c>
+      <c r="P219" s="13" t="s">
         <v>42</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22158,11 +22445,11 @@
       </c>
       <c r="D2" s="11">
         <f>Sheet2!H198</f>
-        <v>0.44967485490095382</v>
+        <v>0.4496749424406794</v>
       </c>
       <c r="E2" s="11">
         <f>Sheet2!I198</f>
-        <v>14.534569120308721</v>
+        <v>14.53456574198389</v>
       </c>
       <c r="F2">
         <f>Sheet2!L198</f>
@@ -22187,11 +22474,11 @@
       </c>
       <c r="D3" s="11">
         <f>Sheet2!H199</f>
-        <v>0.46939788848575226</v>
+        <v>0.46939781890250282</v>
       </c>
       <c r="E3" s="11">
         <f>Sheet2!I199</f>
-        <v>14.536806380218714</v>
+        <v>14.536409496568682</v>
       </c>
       <c r="F3">
         <f>Sheet2!L199</f>
